--- a/Map Entries Progress.xlsx
+++ b/Map Entries Progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnathon\source\repos\legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C845C4F-91C4-4DE0-8407-1BD507ACB98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1820A688-F7A7-41D9-A66E-2F04F8E6F999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{900B916D-4EAF-49F4-8F93-D3AFED532396}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{900B916D-4EAF-49F4-8F93-D3AFED532396}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2679,7 +2679,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2709,8 +2709,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2720,6 +2733,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -2762,9 +2780,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2786,63 +2805,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2895,6 +2867,54 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -2912,212 +2932,28 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BA531307-532A-4CB3-AB97-D9CD6740F5DC}" name="Table1" displayName="Table1" ref="A1:T328" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:T328" xr:uid="{BA531307-532A-4CB3-AB97-D9CD6740F5DC}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="unk_83EE7AC"/>
-        <filter val="unk_83EEA74"/>
-        <filter val="unk_83EEC4C"/>
-        <filter val="unk_83EECCC"/>
-        <filter val="unk_83EED60"/>
-        <filter val="unk_83EEDC8"/>
-        <filter val="unk_83EF44C"/>
-        <filter val="unk_83EF878"/>
-        <filter val="unk_83EFF44"/>
-        <filter val="unk_83F00A8"/>
-        <filter val="unk_83F021C"/>
-        <filter val="unk_83F0674"/>
-        <filter val="unk_83F0AE0"/>
-        <filter val="unk_83F0FD4"/>
-        <filter val="unk_83F128C"/>
-        <filter val="unk_83F13A0"/>
-        <filter val="unk_83F1470"/>
-        <filter val="unk_83F17D0"/>
-        <filter val="unk_83F1B58"/>
-        <filter val="unk_83F1D44"/>
-        <filter val="unk_83F1F34"/>
-        <filter val="unk_83F2130"/>
-        <filter val="unk_83F21E0"/>
-        <filter val="unk_83F25D8"/>
-        <filter val="unk_83F2990"/>
-        <filter val="unk_83F2ACC"/>
-        <filter val="unk_83F2FE4"/>
-        <filter val="unk_83F33B4"/>
-        <filter val="unk_83F3808"/>
-        <filter val="unk_83F3AD8"/>
-        <filter val="unk_83F3EC8"/>
-        <filter val="unk_83F41D4"/>
-        <filter val="unk_83F42D8"/>
-        <filter val="unk_83F43AC"/>
-        <filter val="unk_83F43FC"/>
-        <filter val="unk_83F4444"/>
-        <filter val="unk_83F44A8"/>
-        <filter val="unk_83F4518"/>
-        <filter val="unk_83F4560"/>
-        <filter val="unk_83F45D8"/>
-        <filter val="unk_83F486C"/>
-        <filter val="unk_83F4A44"/>
-        <filter val="unk_83F4AB8"/>
-        <filter val="unk_83F4B64"/>
-        <filter val="unk_83F4BB4"/>
-        <filter val="unk_83F4C98"/>
-        <filter val="unk_83F4D38"/>
-        <filter val="unk_83F4E24"/>
-        <filter val="unk_83F5114"/>
-        <filter val="unk_83F5538"/>
-        <filter val="unk_83F57AC"/>
-        <filter val="unk_83F5F54"/>
-        <filter val="unk_83F6420"/>
-        <filter val="unk_83F6BE4"/>
-        <filter val="unk_83F7628"/>
-        <filter val="unk_83F7FB8"/>
-        <filter val="unk_83F80E4"/>
-        <filter val="unk_83F82B4"/>
-        <filter val="unk_83F8340"/>
-        <filter val="unk_83F835C"/>
-        <filter val="unk_83F8524"/>
-        <filter val="unk_83F8654"/>
-        <filter val="unk_83F88C8"/>
-        <filter val="unk_83F8920"/>
-        <filter val="unk_83F89B0"/>
-        <filter val="unk_83F8A98"/>
-        <filter val="unk_83F8D48"/>
-        <filter val="unk_83F92BC"/>
-        <filter val="unk_83F96A4"/>
-        <filter val="unk_83F98D0"/>
-        <filter val="unk_83F9A0C"/>
-        <filter val="unk_83F9CF8"/>
-        <filter val="unk_83F9E30"/>
-        <filter val="unk_83F9FD0"/>
-        <filter val="unk_83FA048"/>
-        <filter val="unk_83FA338"/>
-        <filter val="unk_83FA370"/>
-        <filter val="unk_83FA45C"/>
-        <filter val="unk_83FA4FC"/>
-        <filter val="unk_83FA66C"/>
-        <filter val="unk_83FA77C"/>
-        <filter val="unk_83FA998"/>
-        <filter val="unk_83FAAE0"/>
-        <filter val="unk_83FAB58"/>
-        <filter val="unk_83FACB8"/>
-        <filter val="unk_83FAD18"/>
-        <filter val="unk_83FAD98"/>
-        <filter val="unk_83FAE68"/>
-        <filter val="unk_83FAED0"/>
-        <filter val="unk_83FAF5C"/>
-        <filter val="unk_83FB130"/>
-        <filter val="unk_83FB178"/>
-        <filter val="unk_83FB284"/>
-        <filter val="unk_83FB5B0"/>
-        <filter val="unk_83FB61C"/>
-        <filter val="unk_83FB80C"/>
-        <filter val="unk_83FBDF8"/>
-        <filter val="unk_83FC084"/>
-        <filter val="unk_83FC7A0"/>
-        <filter val="unk_83FC808"/>
-        <filter val="unk_83FD1A4"/>
-        <filter val="unk_83FD4F8"/>
-        <filter val="unk_83FD6E0"/>
-        <filter val="unk_83FD76C"/>
-        <filter val="unk_83FD820"/>
-        <filter val="unk_83FE4F4"/>
-        <filter val="unk_83FE8A8"/>
-        <filter val="unk_83FF4DC"/>
-        <filter val="unk_83FFCF8"/>
-        <filter val="unk_83FFD9C"/>
-        <filter val="unk_840003C"/>
-        <filter val="unk_8400340"/>
-        <filter val="unk_8400788"/>
-        <filter val="unk_8400D90"/>
-        <filter val="unk_8400FD0"/>
-        <filter val="unk_840148C"/>
-        <filter val="unk_84016A8"/>
-        <filter val="unk_8401738"/>
-        <filter val="unk_8402024"/>
-        <filter val="unk_84020C4"/>
-        <filter val="unk_84024AC"/>
-        <filter val="unk_84026A4"/>
-        <filter val="unk_8402CF4"/>
-        <filter val="unk_8402D88"/>
-        <filter val="unk_8402E00"/>
-        <filter val="unk_8403294"/>
-        <filter val="unk_84033DC"/>
-        <filter val="unk_84035C8"/>
-        <filter val="unk_84039F0"/>
-        <filter val="unk_8403B84"/>
-        <filter val="unk_8403C44"/>
-        <filter val="unk_8403CDC"/>
-        <filter val="unk_8403D3C"/>
-        <filter val="unk_8403DB4"/>
-        <filter val="unk_8403E2C"/>
-        <filter val="unk_8404050"/>
-        <filter val="unk_8404088"/>
-        <filter val="unk_8404280"/>
-        <filter val="unk_8404430"/>
-        <filter val="unk_8404490"/>
-        <filter val="unk_8404794"/>
-        <filter val="unk_840487C"/>
-        <filter val="unk_8404BD0"/>
-        <filter val="unk_8404D08"/>
-        <filter val="unk_84051C4"/>
-        <filter val="unk_84057D4"/>
-        <filter val="unk_8405818"/>
-        <filter val="unk_8405860"/>
-        <filter val="unk_84059BC"/>
-        <filter val="unk_8406048"/>
-        <filter val="unk_8406300"/>
-        <filter val="unk_8406458"/>
-        <filter val="unk_8406518"/>
-        <filter val="unk_8406638"/>
-        <filter val="unk_8406828"/>
-        <filter val="unk_8406B2C"/>
-        <filter val="unk_8406DB0"/>
-        <filter val="unk_8406E4C"/>
-        <filter val="unk_8407050"/>
-        <filter val="unk_8407384"/>
-        <filter val="unk_8407C70"/>
-        <filter val="unk_8407EB4"/>
-        <filter val="unk_84080C0"/>
-        <filter val="unk_8408190"/>
-        <filter val="Z13A3_TriggerArray"/>
-        <filter val="Z13A5_TriggerArray"/>
-        <filter val="Z13A7_TriggerArray"/>
-        <filter val="Z14A1_TriggerArray"/>
-        <filter val="Z14A2_TriggerArray"/>
-        <filter val="Z1A1_TriggerArray"/>
-        <filter val="Z1A2_TriggerArray"/>
-        <filter val="Z1A4_TriggerArray"/>
-        <filter val="Z1A5_TriggerArray"/>
-        <filter val="Z2A1_TriggerArray"/>
-        <filter val="Z2A2_TriggerArray"/>
-        <filter val="Z2A4_TriggerArray"/>
-        <filter val="Z2A5_TriggerArray"/>
-        <filter val="Z2A6_TriggerArray"/>
-        <filter val="Z2A7_TriggerArray"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T328" xr:uid="{BA531307-532A-4CB3-AB97-D9CD6740F5DC}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{8AFDAFB9-D89C-4615-8526-A79F708AAB47}" name="Zone" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{6835433F-9358-4675-A20C-A788D6D3194F}" name="Area" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{3BFDAC4A-4059-4609-9600-26CC129595AD}" name="Variation" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{4C41685F-2AE4-4494-AD88-CE7122C48A41}" name="Trigger Count" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{D17C4F06-897A-4259-86A4-A6049430B561}" name="Script Count" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{8B5500E4-FE87-4AD5-96E2-D1102DFD2A84}" name="Item Count" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{D228D8D8-A919-45E6-B713-AC5463CC568C}" name="Object Count" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{94A87ED6-451C-48F6-948F-4DBD08217D20}" name="NPC Count" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{025999FC-D21D-46C8-97E8-E70D5100E2DE}" name="flags" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{A3F589F9-A7F3-4D76-A60F-E31611B80A67}" name="unk_0C" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{BF7BA013-BDBA-4663-9FFE-3DD600ED6CF6}" name="Map Triggers" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{EA753079-7B70-4658-9F28-431C79BD2FFF}" name="Map Scripts" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{C9A05C75-3AE7-4698-BB90-FA60FBF8288E}" name="Map Items" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{671A4567-C23C-4483-9D83-C3A025CE676D}" name="Map Objects" dataDxfId="10" dataCellStyle="Good"/>
-    <tableColumn id="18" xr3:uid="{53A914CA-F1DC-4CE8-8EB1-0454872BCA58}" name="NPC Array" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{51E38BD3-2ED0-4576-A0A5-FAC85AEFC27C}" name="Music ID" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{A3F62D73-FA5E-46CD-A1EF-CB8D2919E2FE}" name="Variation Script" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{FCA49C89-81A2-406C-AB95-C3F7D8DEAF86}" name="Variation Array" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{2CDEAA0D-F72C-4A80-B93B-CE06FB165B56}" name="Entry Script" dataDxfId="5"/>
-    <tableColumn id="23" xr3:uid="{30FD3892-6D25-4470-AAA6-B1FB53C5B194}" name="Exit Script" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{8AFDAFB9-D89C-4615-8526-A79F708AAB47}" name="Zone" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{6835433F-9358-4675-A20C-A788D6D3194F}" name="Area" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{3BFDAC4A-4059-4609-9600-26CC129595AD}" name="Variation" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{4C41685F-2AE4-4494-AD88-CE7122C48A41}" name="Trigger Count" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{D17C4F06-897A-4259-86A4-A6049430B561}" name="Script Count" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{8B5500E4-FE87-4AD5-96E2-D1102DFD2A84}" name="Item Count" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{D228D8D8-A919-45E6-B713-AC5463CC568C}" name="Object Count" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{94A87ED6-451C-48F6-948F-4DBD08217D20}" name="NPC Count" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{025999FC-D21D-46C8-97E8-E70D5100E2DE}" name="flags" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{A3F589F9-A7F3-4D76-A60F-E31611B80A67}" name="unk_0C" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{BF7BA013-BDBA-4663-9FFE-3DD600ED6CF6}" name="Map Triggers" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{EA753079-7B70-4658-9F28-431C79BD2FFF}" name="Map Scripts" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{C9A05C75-3AE7-4698-BB90-FA60FBF8288E}" name="Map Items" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{671A4567-C23C-4483-9D83-C3A025CE676D}" name="Map Objects" dataDxfId="6" dataCellStyle="Good"/>
+    <tableColumn id="18" xr3:uid="{53A914CA-F1DC-4CE8-8EB1-0454872BCA58}" name="NPC Array" dataDxfId="5"/>
+    <tableColumn id="19" xr3:uid="{51E38BD3-2ED0-4576-A0A5-FAC85AEFC27C}" name="Music ID" dataDxfId="4" dataCellStyle="Good"/>
+    <tableColumn id="20" xr3:uid="{A3F62D73-FA5E-46CD-A1EF-CB8D2919E2FE}" name="Variation Script" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{FCA49C89-81A2-406C-AB95-C3F7D8DEAF86}" name="Variation Array" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{2CDEAA0D-F72C-4A80-B93B-CE06FB165B56}" name="Entry Script" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{30FD3892-6D25-4470-AAA6-B1FB53C5B194}" name="Exit Script" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3440,31 +3276,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459BF501-5189-4BD7-95F3-B37593B3FCA3}">
-  <dimension ref="A1:U328"/>
+  <dimension ref="A1:T328"/>
   <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" style="1" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" style="1" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21" style="1" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="14.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.4">
@@ -3575,7 +3410,7 @@
       <c r="O2" s="1">
         <v>0</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="Q2" s="1">
@@ -3637,7 +3472,7 @@
       <c r="O3" s="1">
         <v>0</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="Q3" s="1">
@@ -3653,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -3699,7 +3534,7 @@
       <c r="O4" s="1">
         <v>0</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>7</v>
       </c>
       <c r="Q4" s="1">
@@ -3761,7 +3596,7 @@
       <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Q5" s="1">
@@ -3823,7 +3658,7 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="P6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="Q6" s="1">
@@ -3839,7 +3674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>1</v>
       </c>
@@ -3885,7 +3720,7 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="P7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="Q7" s="1">
@@ -3901,7 +3736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -3947,7 +3782,7 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="Q8" s="1">
@@ -4009,7 +3844,7 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="P9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="Q9" s="1" t="s">
@@ -4071,7 +3906,7 @@
       <c r="O10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="P10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -4087,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>2</v>
       </c>
@@ -4133,7 +3968,7 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="P11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q11" s="1" t="s">
@@ -4195,7 +4030,7 @@
       <c r="O12" s="1">
         <v>0</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="P12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q12" s="1">
@@ -4257,7 +4092,7 @@
       <c r="O13" s="1">
         <v>0</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="P13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q13" s="1" t="s">
@@ -4319,7 +4154,7 @@
       <c r="O14" s="1">
         <v>0</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="P14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q14" s="1" t="s">
@@ -4381,7 +4216,7 @@
       <c r="O15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="P15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q15" s="1" t="s">
@@ -4443,7 +4278,7 @@
       <c r="O16" s="1">
         <v>0</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>6</v>
       </c>
       <c r="Q16" s="1">
@@ -4459,7 +4294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>2</v>
       </c>
@@ -4505,7 +4340,7 @@
       <c r="O17" s="1">
         <v>0</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="P17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q17" s="1" t="s">
@@ -4521,7 +4356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>2</v>
       </c>
@@ -4567,7 +4402,7 @@
       <c r="O18" s="1">
         <v>0</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="P18" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q18" s="1">
@@ -4629,7 +4464,7 @@
       <c r="O19" s="1">
         <v>0</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="P19" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q19" s="1">
@@ -4691,7 +4526,7 @@
       <c r="O20" s="1">
         <v>0</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="P20" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q20" s="1">
@@ -4753,7 +4588,7 @@
       <c r="O21" s="1">
         <v>0</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="P21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q21" s="1" t="s">
@@ -4815,7 +4650,7 @@
       <c r="O22" s="1">
         <v>0</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="P22" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q22" s="1">
@@ -4878,7 +4713,7 @@
       <c r="O23" s="1">
         <v>0</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="P23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q23" s="1">
@@ -4895,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>2</v>
       </c>
@@ -4926,7 +4761,7 @@
       <c r="J24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="2">
         <v>0</v>
       </c>
       <c r="L24" s="1" t="s">
@@ -4941,7 +4776,7 @@
       <c r="O24" s="1">
         <v>0</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>3</v>
       </c>
       <c r="Q24" s="1">
@@ -4958,7 +4793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
         <v>2</v>
       </c>
@@ -4989,7 +4824,7 @@
       <c r="J25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="2">
         <v>0</v>
       </c>
       <c r="L25" s="1" t="s">
@@ -5004,7 +4839,7 @@
       <c r="O25" s="1">
         <v>0</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>3</v>
       </c>
       <c r="Q25" s="1">
@@ -5021,7 +4856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
         <v>2</v>
       </c>
@@ -5052,7 +4887,7 @@
       <c r="J26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="2">
         <v>0</v>
       </c>
       <c r="L26" s="1" t="s">
@@ -5067,7 +4902,7 @@
       <c r="O26" s="1">
         <v>0</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>3</v>
       </c>
       <c r="Q26" s="1">
@@ -5130,7 +4965,7 @@
       <c r="O27" s="1">
         <v>0</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>3</v>
       </c>
       <c r="Q27" s="1">
@@ -5147,7 +4982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A28" s="4">
         <v>2</v>
       </c>
@@ -5178,7 +5013,7 @@
       <c r="J28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K28" s="2">
         <v>0</v>
       </c>
       <c r="L28" s="1" t="s">
@@ -5193,7 +5028,7 @@
       <c r="O28" s="1">
         <v>0</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>3</v>
       </c>
       <c r="Q28" s="1">
@@ -5210,7 +5045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A29" s="4">
         <v>2</v>
       </c>
@@ -5241,7 +5076,7 @@
       <c r="J29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29" s="2">
         <v>0</v>
       </c>
       <c r="L29" s="1" t="s">
@@ -5256,7 +5091,7 @@
       <c r="O29" s="1">
         <v>0</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>3</v>
       </c>
       <c r="Q29" s="1">
@@ -5319,7 +5154,7 @@
       <c r="O30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="2">
         <v>3</v>
       </c>
       <c r="Q30" s="1">
@@ -5336,7 +5171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A31" s="4">
         <v>2</v>
       </c>
@@ -5367,7 +5202,7 @@
       <c r="J31" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K31" s="2">
         <v>0</v>
       </c>
       <c r="L31" s="1" t="s">
@@ -5382,7 +5217,7 @@
       <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="2">
         <v>3</v>
       </c>
       <c r="Q31" s="1">
@@ -5399,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A32" s="4">
         <v>2</v>
       </c>
@@ -5430,7 +5265,7 @@
       <c r="J32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K32" s="2">
         <v>0</v>
       </c>
       <c r="L32" s="1" t="s">
@@ -5445,7 +5280,7 @@
       <c r="O32" s="1">
         <v>0</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="2">
         <v>3</v>
       </c>
       <c r="Q32" s="1">
@@ -5462,7 +5297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A33" s="4">
         <v>2</v>
       </c>
@@ -5493,7 +5328,7 @@
       <c r="J33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K33" s="2">
         <v>0</v>
       </c>
       <c r="L33" s="1" t="s">
@@ -5508,7 +5343,7 @@
       <c r="O33" s="1">
         <v>0</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>3</v>
       </c>
       <c r="Q33" s="1">
@@ -5525,7 +5360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A34" s="4">
         <v>2</v>
       </c>
@@ -5556,7 +5391,7 @@
       <c r="J34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K34" s="2">
         <v>0</v>
       </c>
       <c r="L34" s="1" t="s">
@@ -5571,7 +5406,7 @@
       <c r="O34" s="1">
         <v>0</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>3</v>
       </c>
       <c r="Q34" s="1">
@@ -5588,7 +5423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A35" s="4">
         <v>2</v>
       </c>
@@ -5619,7 +5454,7 @@
       <c r="J35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="2">
         <v>0</v>
       </c>
       <c r="L35" s="1" t="s">
@@ -5634,7 +5469,7 @@
       <c r="O35" s="1">
         <v>0</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>3</v>
       </c>
       <c r="Q35" s="1">
@@ -5651,7 +5486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A36" s="4">
         <v>2</v>
       </c>
@@ -5682,7 +5517,7 @@
       <c r="J36" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K36" s="2">
         <v>0</v>
       </c>
       <c r="L36" s="1" t="s">
@@ -5697,7 +5532,7 @@
       <c r="O36" s="1">
         <v>0</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>3</v>
       </c>
       <c r="Q36" s="1">
@@ -5760,7 +5595,7 @@
       <c r="O37" s="1">
         <v>0</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>3</v>
       </c>
       <c r="Q37" s="1">
@@ -5823,7 +5658,7 @@
       <c r="O38" s="1">
         <v>0</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>3</v>
       </c>
       <c r="Q38" s="1">
@@ -5886,7 +5721,7 @@
       <c r="O39" s="1">
         <v>0</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>3</v>
       </c>
       <c r="Q39" s="1">
@@ -5949,7 +5784,7 @@
       <c r="O40" s="1">
         <v>0</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>3</v>
       </c>
       <c r="Q40" s="1">
@@ -6012,7 +5847,7 @@
       <c r="O41" s="1">
         <v>0</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="2">
         <v>3</v>
       </c>
       <c r="Q41" s="1">
@@ -6075,7 +5910,7 @@
       <c r="O42" s="1">
         <v>0</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="2">
         <v>3</v>
       </c>
       <c r="Q42" s="1">
@@ -6092,7 +5927,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A43" s="4">
         <v>2</v>
       </c>
@@ -6123,7 +5958,7 @@
       <c r="J43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K43" s="2">
         <v>0</v>
       </c>
       <c r="L43" s="1" t="s">
@@ -6138,7 +5973,7 @@
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="2">
         <v>3</v>
       </c>
       <c r="Q43" s="1">
@@ -6155,7 +5990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A44" s="4">
         <v>2</v>
       </c>
@@ -6186,7 +6021,7 @@
       <c r="J44" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K44" s="2">
         <v>0</v>
       </c>
       <c r="L44" s="1" t="s">
@@ -6201,7 +6036,7 @@
       <c r="O44" s="1">
         <v>0</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="2">
         <v>3</v>
       </c>
       <c r="Q44" s="1">
@@ -6218,7 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A45" s="4">
         <v>2</v>
       </c>
@@ -6249,7 +6084,7 @@
       <c r="J45" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K45" s="2">
         <v>0</v>
       </c>
       <c r="L45" s="1" t="s">
@@ -6264,7 +6099,7 @@
       <c r="O45" s="1">
         <v>0</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="2">
         <v>3</v>
       </c>
       <c r="Q45" s="1">
@@ -6281,7 +6116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A46" s="4">
         <v>2</v>
       </c>
@@ -6312,7 +6147,7 @@
       <c r="J46" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K46" s="1">
+      <c r="K46" s="2">
         <v>0</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6327,7 +6162,7 @@
       <c r="O46" s="1">
         <v>0</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="2">
         <v>3</v>
       </c>
       <c r="Q46" s="1">
@@ -6344,7 +6179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A47" s="4">
         <v>2</v>
       </c>
@@ -6375,7 +6210,7 @@
       <c r="J47" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K47" s="2">
         <v>0</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6390,7 +6225,7 @@
       <c r="O47" s="1">
         <v>0</v>
       </c>
-      <c r="P47" s="1">
+      <c r="P47" s="2">
         <v>3</v>
       </c>
       <c r="Q47" s="1">
@@ -6453,7 +6288,7 @@
       <c r="O48" s="1">
         <v>0</v>
       </c>
-      <c r="P48" s="1" t="s">
+      <c r="P48" s="2" t="s">
         <v>146</v>
       </c>
       <c r="Q48" s="1">
@@ -6516,7 +6351,7 @@
       <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="P49" s="1">
+      <c r="P49" s="2">
         <v>3</v>
       </c>
       <c r="Q49" s="1">
@@ -6579,7 +6414,7 @@
       <c r="O50" s="1">
         <v>0</v>
       </c>
-      <c r="P50" s="1">
+      <c r="P50" s="2">
         <v>3</v>
       </c>
       <c r="Q50" s="1">
@@ -6642,7 +6477,7 @@
       <c r="O51" s="1">
         <v>0</v>
       </c>
-      <c r="P51" s="1">
+      <c r="P51" s="2">
         <v>0</v>
       </c>
       <c r="Q51" s="1">
@@ -6659,7 +6494,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A52" s="4">
         <v>3</v>
       </c>
@@ -6690,7 +6525,7 @@
       <c r="J52" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K52" s="1">
+      <c r="K52" s="2">
         <v>0</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6705,7 +6540,7 @@
       <c r="O52" s="1">
         <v>0</v>
       </c>
-      <c r="P52" s="1">
+      <c r="P52" s="2">
         <v>0</v>
       </c>
       <c r="Q52" s="1">
@@ -6768,7 +6603,7 @@
       <c r="O53" s="1">
         <v>0</v>
       </c>
-      <c r="P53" s="1" t="s">
+      <c r="P53" s="2" t="s">
         <v>163</v>
       </c>
       <c r="Q53" s="1">
@@ -6831,7 +6666,7 @@
       <c r="O54" s="1">
         <v>0</v>
       </c>
-      <c r="P54" s="1" t="s">
+      <c r="P54" s="2" t="s">
         <v>166</v>
       </c>
       <c r="Q54" s="1">
@@ -6848,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A55" s="4">
         <v>3</v>
       </c>
@@ -6879,7 +6714,7 @@
       <c r="J55" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K55" s="1">
+      <c r="K55" s="2">
         <v>0</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6894,7 +6729,7 @@
       <c r="O55" s="1">
         <v>0</v>
       </c>
-      <c r="P55" s="1">
+      <c r="P55" s="2">
         <v>6</v>
       </c>
       <c r="Q55" s="1">
@@ -6957,7 +6792,7 @@
       <c r="O56" s="1">
         <v>0</v>
       </c>
-      <c r="P56" s="1">
+      <c r="P56" s="2">
         <v>6</v>
       </c>
       <c r="Q56" s="1">
@@ -7020,7 +6855,7 @@
       <c r="O57" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="P57" s="1">
+      <c r="P57" s="2">
         <v>0</v>
       </c>
       <c r="Q57" s="1">
@@ -7083,7 +6918,7 @@
       <c r="O58" s="1">
         <v>0</v>
       </c>
-      <c r="P58" s="1">
+      <c r="P58" s="2">
         <v>0</v>
       </c>
       <c r="Q58" s="1">
@@ -7146,7 +6981,7 @@
       <c r="O59" s="1">
         <v>0</v>
       </c>
-      <c r="P59" s="1" t="s">
+      <c r="P59" s="2" t="s">
         <v>166</v>
       </c>
       <c r="Q59" s="1">
@@ -7163,7 +6998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A60" s="4">
         <v>3</v>
       </c>
@@ -7194,7 +7029,7 @@
       <c r="J60" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K60" s="1">
+      <c r="K60" s="2">
         <v>0</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -7209,7 +7044,7 @@
       <c r="O60" s="1">
         <v>0</v>
       </c>
-      <c r="P60" s="1">
+      <c r="P60" s="2">
         <v>0</v>
       </c>
       <c r="Q60" s="1">
@@ -7226,7 +7061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A61" s="4">
         <v>3</v>
       </c>
@@ -7257,7 +7092,7 @@
       <c r="J61" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K61" s="1">
+      <c r="K61" s="2">
         <v>0</v>
       </c>
       <c r="L61" s="1" t="s">
@@ -7272,7 +7107,7 @@
       <c r="O61" s="1">
         <v>0</v>
       </c>
-      <c r="P61" s="1">
+      <c r="P61" s="2">
         <v>0</v>
       </c>
       <c r="Q61" s="1">
@@ -7335,7 +7170,7 @@
       <c r="O62" s="1">
         <v>0</v>
       </c>
-      <c r="P62" s="1">
+      <c r="P62" s="2">
         <v>0</v>
       </c>
       <c r="Q62" s="1">
@@ -7352,7 +7187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A63" s="4">
         <v>3</v>
       </c>
@@ -7383,7 +7218,7 @@
       <c r="J63" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K63" s="1">
+      <c r="K63" s="2">
         <v>0</v>
       </c>
       <c r="L63" s="1">
@@ -7398,7 +7233,7 @@
       <c r="O63" s="1">
         <v>0</v>
       </c>
-      <c r="P63" s="1">
+      <c r="P63" s="2">
         <v>0</v>
       </c>
       <c r="Q63" s="1">
@@ -7461,7 +7296,7 @@
       <c r="O64" s="1">
         <v>0</v>
       </c>
-      <c r="P64" s="1">
+      <c r="P64" s="2">
         <v>0</v>
       </c>
       <c r="Q64" s="1">
@@ -7524,7 +7359,7 @@
       <c r="O65" s="1">
         <v>0</v>
       </c>
-      <c r="P65" s="1" t="s">
+      <c r="P65" s="2" t="s">
         <v>195</v>
       </c>
       <c r="Q65" s="1">
@@ -7587,7 +7422,7 @@
       <c r="O66" s="1">
         <v>0</v>
       </c>
-      <c r="P66" s="1" t="s">
+      <c r="P66" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q66" s="1">
@@ -7650,7 +7485,7 @@
       <c r="O67" s="1">
         <v>0</v>
       </c>
-      <c r="P67" s="1" t="s">
+      <c r="P67" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q67" s="1">
@@ -7713,7 +7548,7 @@
       <c r="O68" s="1">
         <v>0</v>
       </c>
-      <c r="P68" s="1" t="s">
+      <c r="P68" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q68" s="1">
@@ -7776,7 +7611,7 @@
       <c r="O69" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="P69" s="1" t="s">
+      <c r="P69" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q69" s="1">
@@ -7839,7 +7674,7 @@
       <c r="O70" s="1">
         <v>0</v>
       </c>
-      <c r="P70" s="1" t="s">
+      <c r="P70" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q70" s="1">
@@ -7856,7 +7691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A71" s="4">
         <v>4</v>
       </c>
@@ -7887,7 +7722,7 @@
       <c r="J71" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K71" s="1">
+      <c r="K71" s="2">
         <v>0</v>
       </c>
       <c r="L71" s="1">
@@ -7902,7 +7737,7 @@
       <c r="O71" s="1">
         <v>0</v>
       </c>
-      <c r="P71" s="1" t="s">
+      <c r="P71" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q71" s="1">
@@ -7919,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A72" s="4">
         <v>4</v>
       </c>
@@ -7950,7 +7785,7 @@
       <c r="J72" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K72" s="1">
+      <c r="K72" s="2">
         <v>0</v>
       </c>
       <c r="L72" s="1">
@@ -7965,7 +7800,7 @@
       <c r="O72" s="1">
         <v>0</v>
       </c>
-      <c r="P72" s="1" t="s">
+      <c r="P72" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q72" s="1">
@@ -7982,7 +7817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A73" s="4">
         <v>4</v>
       </c>
@@ -8013,7 +7848,7 @@
       <c r="J73" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K73" s="1">
+      <c r="K73" s="2">
         <v>0</v>
       </c>
       <c r="L73" s="1">
@@ -8028,7 +7863,7 @@
       <c r="O73" s="1">
         <v>0</v>
       </c>
-      <c r="P73" s="1" t="s">
+      <c r="P73" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q73" s="1">
@@ -8045,7 +7880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A74" s="4">
         <v>4</v>
       </c>
@@ -8076,7 +7911,7 @@
       <c r="J74" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K74" s="1">
+      <c r="K74" s="2">
         <v>0</v>
       </c>
       <c r="L74" s="1">
@@ -8091,7 +7926,7 @@
       <c r="O74" s="1">
         <v>0</v>
       </c>
-      <c r="P74" s="1" t="s">
+      <c r="P74" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q74" s="1">
@@ -8108,7 +7943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A75" s="4">
         <v>4</v>
       </c>
@@ -8139,7 +7974,7 @@
       <c r="J75" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K75" s="1">
+      <c r="K75" s="2">
         <v>0</v>
       </c>
       <c r="L75" s="1">
@@ -8154,7 +7989,7 @@
       <c r="O75" s="1">
         <v>0</v>
       </c>
-      <c r="P75" s="1" t="s">
+      <c r="P75" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q75" s="1">
@@ -8171,7 +8006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A76" s="4">
         <v>4</v>
       </c>
@@ -8202,7 +8037,7 @@
       <c r="J76" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K76" s="1">
+      <c r="K76" s="2">
         <v>0</v>
       </c>
       <c r="L76" s="1">
@@ -8217,7 +8052,7 @@
       <c r="O76" s="1">
         <v>0</v>
       </c>
-      <c r="P76" s="1" t="s">
+      <c r="P76" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q76" s="1">
@@ -8234,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A77" s="4">
         <v>4</v>
       </c>
@@ -8265,7 +8100,7 @@
       <c r="J77" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K77" s="1">
+      <c r="K77" s="2">
         <v>0</v>
       </c>
       <c r="L77" s="1">
@@ -8280,7 +8115,7 @@
       <c r="O77" s="1">
         <v>0</v>
       </c>
-      <c r="P77" s="1" t="s">
+      <c r="P77" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q77" s="1">
@@ -8297,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A78" s="4">
         <v>4</v>
       </c>
@@ -8328,7 +8163,7 @@
       <c r="J78" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K78" s="1">
+      <c r="K78" s="2">
         <v>0</v>
       </c>
       <c r="L78" s="1">
@@ -8343,7 +8178,7 @@
       <c r="O78" s="1">
         <v>0</v>
       </c>
-      <c r="P78" s="1" t="s">
+      <c r="P78" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q78" s="1">
@@ -8360,7 +8195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A79" s="4">
         <v>4</v>
       </c>
@@ -8391,7 +8226,7 @@
       <c r="J79" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K79" s="1">
+      <c r="K79" s="2">
         <v>0</v>
       </c>
       <c r="L79" s="1">
@@ -8406,7 +8241,7 @@
       <c r="O79" s="1">
         <v>0</v>
       </c>
-      <c r="P79" s="1" t="s">
+      <c r="P79" s="2" t="s">
         <v>214</v>
       </c>
       <c r="Q79" s="1">
@@ -8454,7 +8289,7 @@
       <c r="J80" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K80" s="2" t="s">
         <v>216</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -8469,7 +8304,7 @@
       <c r="O80" s="1">
         <v>0</v>
       </c>
-      <c r="P80" s="1" t="s">
+      <c r="P80" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q80" s="1">
@@ -8486,7 +8321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A81" s="4">
         <v>4</v>
       </c>
@@ -8517,7 +8352,7 @@
       <c r="J81" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="K81" s="1">
+      <c r="K81" s="2">
         <v>0</v>
       </c>
       <c r="L81" s="1">
@@ -8532,7 +8367,7 @@
       <c r="O81" s="1">
         <v>0</v>
       </c>
-      <c r="P81" s="1" t="s">
+      <c r="P81" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q81" s="1">
@@ -8580,7 +8415,7 @@
       <c r="J82" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="K82" s="2" t="s">
         <v>220</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -8595,7 +8430,7 @@
       <c r="O82" s="1">
         <v>0</v>
       </c>
-      <c r="P82" s="1" t="s">
+      <c r="P82" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q82" s="1">
@@ -8643,7 +8478,7 @@
       <c r="J83" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="K83" s="3" t="s">
         <v>223</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -8658,7 +8493,7 @@
       <c r="O83" s="1">
         <v>0</v>
       </c>
-      <c r="P83" s="1" t="s">
+      <c r="P83" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q83" s="1">
@@ -8706,7 +8541,7 @@
       <c r="J84" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K84" s="2" t="s">
         <v>225</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -8721,7 +8556,7 @@
       <c r="O84" s="1">
         <v>0</v>
       </c>
-      <c r="P84" s="1" t="s">
+      <c r="P84" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q84" s="1">
@@ -8769,7 +8604,7 @@
       <c r="J85" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K85" s="2" t="s">
         <v>228</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -8784,7 +8619,7 @@
       <c r="O85" s="1">
         <v>0</v>
       </c>
-      <c r="P85" s="1" t="s">
+      <c r="P85" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q85" s="1">
@@ -8832,7 +8667,7 @@
       <c r="J86" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K86" s="2" t="s">
         <v>230</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -8847,7 +8682,7 @@
       <c r="O86" s="1">
         <v>0</v>
       </c>
-      <c r="P86" s="1" t="s">
+      <c r="P86" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q86" s="1">
@@ -8895,7 +8730,7 @@
       <c r="J87" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K87" s="2" t="s">
         <v>232</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -8910,7 +8745,7 @@
       <c r="O87" s="1">
         <v>0</v>
       </c>
-      <c r="P87" s="1" t="s">
+      <c r="P87" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q87" s="1">
@@ -8958,7 +8793,7 @@
       <c r="J88" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K88" s="2" t="s">
         <v>235</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -8973,7 +8808,7 @@
       <c r="O88" s="1">
         <v>0</v>
       </c>
-      <c r="P88" s="1" t="s">
+      <c r="P88" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q88" s="1">
@@ -8990,7 +8825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A89" s="4">
         <v>4</v>
       </c>
@@ -9021,7 +8856,7 @@
       <c r="J89" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K89" s="1">
+      <c r="K89" s="2">
         <v>0</v>
       </c>
       <c r="L89" s="1">
@@ -9036,7 +8871,7 @@
       <c r="O89" s="1">
         <v>0</v>
       </c>
-      <c r="P89" s="1" t="s">
+      <c r="P89" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q89" s="1">
@@ -9053,7 +8888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A90" s="4">
         <v>4</v>
       </c>
@@ -9084,7 +8919,7 @@
       <c r="J90" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K90" s="1">
+      <c r="K90" s="2">
         <v>0</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -9099,7 +8934,7 @@
       <c r="O90" s="1">
         <v>0</v>
       </c>
-      <c r="P90" s="1" t="s">
+      <c r="P90" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q90" s="1">
@@ -9116,7 +8951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A91" s="4">
         <v>4</v>
       </c>
@@ -9147,7 +8982,7 @@
       <c r="J91" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K91" s="1">
+      <c r="K91" s="2">
         <v>0</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -9162,7 +8997,7 @@
       <c r="O91" s="1">
         <v>0</v>
       </c>
-      <c r="P91" s="1" t="s">
+      <c r="P91" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q91" s="1">
@@ -9210,7 +9045,7 @@
       <c r="J92" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K92" s="3" t="s">
         <v>240</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -9225,7 +9060,7 @@
       <c r="O92" s="1">
         <v>0</v>
       </c>
-      <c r="P92" s="1">
+      <c r="P92" s="2">
         <v>9</v>
       </c>
       <c r="Q92" s="1">
@@ -9273,7 +9108,7 @@
       <c r="J93" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K93" s="2" t="s">
         <v>243</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -9288,7 +9123,7 @@
       <c r="O93" s="1">
         <v>0</v>
       </c>
-      <c r="P93" s="1" t="s">
+      <c r="P93" s="2" t="s">
         <v>214</v>
       </c>
       <c r="Q93" s="1">
@@ -9336,7 +9171,7 @@
       <c r="J94" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="K94" s="2" t="s">
         <v>246</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -9351,7 +9186,7 @@
       <c r="O94" s="1">
         <v>0</v>
       </c>
-      <c r="P94" s="1">
+      <c r="P94" s="2">
         <v>9</v>
       </c>
       <c r="Q94" s="1">
@@ -9399,7 +9234,7 @@
       <c r="J95" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="K95" s="2" t="s">
         <v>249</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -9414,7 +9249,7 @@
       <c r="O95" s="1">
         <v>0</v>
       </c>
-      <c r="P95" s="1">
+      <c r="P95" s="2">
         <v>9</v>
       </c>
       <c r="Q95" s="1">
@@ -9462,7 +9297,7 @@
       <c r="J96" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="K96" s="2" t="s">
         <v>251</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -9477,7 +9312,7 @@
       <c r="O96" s="1">
         <v>0</v>
       </c>
-      <c r="P96" s="1" t="s">
+      <c r="P96" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Q96" s="1">
@@ -9525,7 +9360,7 @@
       <c r="J97" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="K97" s="2" t="s">
         <v>254</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -9540,7 +9375,7 @@
       <c r="O97" s="1">
         <v>0</v>
       </c>
-      <c r="P97" s="1" t="s">
+      <c r="P97" s="2" t="s">
         <v>214</v>
       </c>
       <c r="Q97" s="1">
@@ -9588,7 +9423,7 @@
       <c r="J98" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="K98" s="2" t="s">
         <v>257</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -9603,7 +9438,7 @@
       <c r="O98" s="1">
         <v>0</v>
       </c>
-      <c r="P98" s="1" t="s">
+      <c r="P98" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q98" s="1">
@@ -9651,7 +9486,7 @@
       <c r="J99" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="K99" s="2" t="s">
         <v>262</v>
       </c>
       <c r="L99" s="1">
@@ -9666,7 +9501,7 @@
       <c r="O99" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="P99" s="1" t="s">
+      <c r="P99" s="2" t="s">
         <v>265</v>
       </c>
       <c r="Q99" s="1">
@@ -9714,7 +9549,7 @@
       <c r="J100" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="K100" s="2" t="s">
         <v>267</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -9729,7 +9564,7 @@
       <c r="O100" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P100" s="1">
+      <c r="P100" s="2">
         <v>0</v>
       </c>
       <c r="Q100" s="1">
@@ -9746,7 +9581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A101" s="4">
         <v>4</v>
       </c>
@@ -9777,7 +9612,7 @@
       <c r="J101" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K101" s="1">
+      <c r="K101" s="2">
         <v>0</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -9792,7 +9627,7 @@
       <c r="O101" s="1">
         <v>0</v>
       </c>
-      <c r="P101" s="1">
+      <c r="P101" s="2">
         <v>0</v>
       </c>
       <c r="Q101" s="1">
@@ -9840,7 +9675,7 @@
       <c r="J102" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K102" s="2" t="s">
         <v>276</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -9855,7 +9690,7 @@
       <c r="O102" s="1">
         <v>0</v>
       </c>
-      <c r="P102" s="1">
+      <c r="P102" s="2">
         <v>0</v>
       </c>
       <c r="Q102" s="1">
@@ -9872,7 +9707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A103" s="4">
         <v>4</v>
       </c>
@@ -9903,7 +9738,7 @@
       <c r="J103" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K103" s="1">
+      <c r="K103" s="2">
         <v>0</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -9918,7 +9753,7 @@
       <c r="O103" s="1">
         <v>0</v>
       </c>
-      <c r="P103" s="1">
+      <c r="P103" s="2">
         <v>0</v>
       </c>
       <c r="Q103" s="1">
@@ -9966,7 +9801,7 @@
       <c r="J104" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K104" s="2" t="s">
         <v>283</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -9981,7 +9816,7 @@
       <c r="O104" s="1">
         <v>0</v>
       </c>
-      <c r="P104" s="1">
+      <c r="P104" s="2">
         <v>0</v>
       </c>
       <c r="Q104" s="1">
@@ -10029,7 +9864,7 @@
       <c r="J105" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K105" s="2" t="s">
         <v>288</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -10044,7 +9879,7 @@
       <c r="O105" s="1">
         <v>0</v>
       </c>
-      <c r="P105" s="1" t="s">
+      <c r="P105" s="2" t="s">
         <v>290</v>
       </c>
       <c r="Q105" s="1" t="s">
@@ -10061,7 +9896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A106" s="4">
         <v>4</v>
       </c>
@@ -10092,7 +9927,7 @@
       <c r="J106" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K106" s="1">
+      <c r="K106" s="2">
         <v>0</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -10107,7 +9942,7 @@
       <c r="O106" s="1">
         <v>0</v>
       </c>
-      <c r="P106" s="1">
+      <c r="P106" s="2">
         <v>0</v>
       </c>
       <c r="Q106" s="1">
@@ -10155,7 +9990,7 @@
       <c r="J107" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K107" s="1" t="s">
+      <c r="K107" s="2" t="s">
         <v>293</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -10170,7 +10005,7 @@
       <c r="O107" s="1">
         <v>0</v>
       </c>
-      <c r="P107" s="1" t="s">
+      <c r="P107" s="2" t="s">
         <v>296</v>
       </c>
       <c r="Q107" s="1">
@@ -10187,7 +10022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A108" s="4">
         <v>4</v>
       </c>
@@ -10218,7 +10053,7 @@
       <c r="J108" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K108" s="1">
+      <c r="K108" s="2">
         <v>0</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -10233,7 +10068,7 @@
       <c r="O108" s="1">
         <v>0</v>
       </c>
-      <c r="P108" s="1">
+      <c r="P108" s="2">
         <v>0</v>
       </c>
       <c r="Q108" s="1">
@@ -10250,7 +10085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A109" s="4">
         <v>4</v>
       </c>
@@ -10281,7 +10116,7 @@
       <c r="J109" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="K109" s="1">
+      <c r="K109" s="2">
         <v>0</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -10296,7 +10131,7 @@
       <c r="O109" s="1">
         <v>0</v>
       </c>
-      <c r="P109" s="1" t="s">
+      <c r="P109" s="2" t="s">
         <v>300</v>
       </c>
       <c r="Q109" s="1">
@@ -10313,7 +10148,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A110" s="4">
         <v>4</v>
       </c>
@@ -10344,7 +10179,7 @@
       <c r="J110" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="K110" s="1">
+      <c r="K110" s="2">
         <v>0</v>
       </c>
       <c r="L110" s="1">
@@ -10359,7 +10194,7 @@
       <c r="O110" s="1">
         <v>0</v>
       </c>
-      <c r="P110" s="1" t="s">
+      <c r="P110" s="2" t="s">
         <v>300</v>
       </c>
       <c r="Q110" s="1">
@@ -10376,7 +10211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A111" s="4">
         <v>4</v>
       </c>
@@ -10407,7 +10242,7 @@
       <c r="J111" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="K111" s="1">
+      <c r="K111" s="2">
         <v>0</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -10422,7 +10257,7 @@
       <c r="O111" s="1">
         <v>0</v>
       </c>
-      <c r="P111" s="1" t="s">
+      <c r="P111" s="2" t="s">
         <v>300</v>
       </c>
       <c r="Q111" s="1">
@@ -10439,7 +10274,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A112" s="4">
         <v>4</v>
       </c>
@@ -10470,7 +10305,7 @@
       <c r="J112" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="K112" s="1">
+      <c r="K112" s="2">
         <v>0</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -10485,7 +10320,7 @@
       <c r="O112" s="1">
         <v>0</v>
       </c>
-      <c r="P112" s="1" t="s">
+      <c r="P112" s="2" t="s">
         <v>300</v>
       </c>
       <c r="Q112" s="1">
@@ -10533,7 +10368,7 @@
       <c r="J113" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K113" s="1" t="s">
+      <c r="K113" s="2" t="s">
         <v>306</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -10548,7 +10383,7 @@
       <c r="O113" s="1">
         <v>0</v>
       </c>
-      <c r="P113" s="1">
+      <c r="P113" s="2">
         <v>6</v>
       </c>
       <c r="Q113" s="1">
@@ -10565,7 +10400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A114" s="4">
         <v>4</v>
       </c>
@@ -10596,7 +10431,7 @@
       <c r="J114" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K114" s="1">
+      <c r="K114" s="2">
         <v>0</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -10611,7 +10446,7 @@
       <c r="O114" s="1">
         <v>0</v>
       </c>
-      <c r="P114" s="1" t="s">
+      <c r="P114" s="2" t="s">
         <v>311</v>
       </c>
       <c r="Q114" s="1">
@@ -10659,7 +10494,7 @@
       <c r="J115" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K115" s="1" t="s">
+      <c r="K115" s="2" t="s">
         <v>312</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -10674,7 +10509,7 @@
       <c r="O115" s="1">
         <v>0</v>
       </c>
-      <c r="P115" s="1" t="s">
+      <c r="P115" s="2" t="s">
         <v>311</v>
       </c>
       <c r="Q115" s="1">
@@ -10691,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A116" s="4">
         <v>4</v>
       </c>
@@ -10722,7 +10557,7 @@
       <c r="J116" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K116" s="1">
+      <c r="K116" s="2">
         <v>0</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -10737,7 +10572,7 @@
       <c r="O116" s="1">
         <v>0</v>
       </c>
-      <c r="P116" s="1" t="s">
+      <c r="P116" s="2" t="s">
         <v>311</v>
       </c>
       <c r="Q116" s="1">
@@ -10754,7 +10589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A117" s="4">
         <v>4</v>
       </c>
@@ -10785,7 +10620,7 @@
       <c r="J117" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K117" s="1">
+      <c r="K117" s="2">
         <v>0</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -10800,7 +10635,7 @@
       <c r="O117" s="1">
         <v>0</v>
       </c>
-      <c r="P117" s="1" t="s">
+      <c r="P117" s="2" t="s">
         <v>311</v>
       </c>
       <c r="Q117" s="1">
@@ -10817,7 +10652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A118" s="4">
         <v>4</v>
       </c>
@@ -10848,7 +10683,7 @@
       <c r="J118" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K118" s="1">
+      <c r="K118" s="2">
         <v>0</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -10863,7 +10698,7 @@
       <c r="O118" s="1">
         <v>0</v>
       </c>
-      <c r="P118" s="1" t="s">
+      <c r="P118" s="2" t="s">
         <v>311</v>
       </c>
       <c r="Q118" s="1">
@@ -10911,7 +10746,7 @@
       <c r="J119" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="K119" s="1" t="s">
+      <c r="K119" s="2" t="s">
         <v>322</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -10926,7 +10761,7 @@
       <c r="O119" s="1">
         <v>0</v>
       </c>
-      <c r="P119" s="1" t="s">
+      <c r="P119" s="2" t="s">
         <v>326</v>
       </c>
       <c r="Q119" s="1">
@@ -10974,7 +10809,7 @@
       <c r="J120" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="K120" s="2" t="s">
         <v>327</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -10989,7 +10824,7 @@
       <c r="O120" s="1">
         <v>0</v>
       </c>
-      <c r="P120" s="1" t="s">
+      <c r="P120" s="2" t="s">
         <v>311</v>
       </c>
       <c r="Q120" s="1">
@@ -11037,7 +10872,7 @@
       <c r="J121" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="K121" s="2" t="s">
         <v>330</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -11052,7 +10887,7 @@
       <c r="O121" s="1">
         <v>0</v>
       </c>
-      <c r="P121" s="1">
+      <c r="P121" s="2">
         <v>9</v>
       </c>
       <c r="Q121" s="1">
@@ -11069,7 +10904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A122" s="4">
         <v>4</v>
       </c>
@@ -11100,7 +10935,7 @@
       <c r="J122" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="K122" s="1">
+      <c r="K122" s="2">
         <v>0</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -11115,7 +10950,7 @@
       <c r="O122" s="1">
         <v>0</v>
       </c>
-      <c r="P122" s="1" t="s">
+      <c r="P122" s="2" t="s">
         <v>326</v>
       </c>
       <c r="Q122" s="1">
@@ -11163,7 +10998,7 @@
       <c r="J123" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K123" s="1" t="s">
+      <c r="K123" s="2" t="s">
         <v>335</v>
       </c>
       <c r="L123" s="1">
@@ -11178,7 +11013,7 @@
       <c r="O123" s="1">
         <v>0</v>
       </c>
-      <c r="P123" s="1">
+      <c r="P123" s="2">
         <v>9</v>
       </c>
       <c r="Q123" s="1">
@@ -11226,7 +11061,7 @@
       <c r="J124" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K124" s="1" t="s">
+      <c r="K124" s="2" t="s">
         <v>338</v>
       </c>
       <c r="L124" s="1">
@@ -11241,7 +11076,7 @@
       <c r="O124" s="1">
         <v>0</v>
       </c>
-      <c r="P124" s="1">
+      <c r="P124" s="2">
         <v>0</v>
       </c>
       <c r="Q124" s="1">
@@ -11258,7 +11093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A125" s="4">
         <v>4</v>
       </c>
@@ -11289,7 +11124,7 @@
       <c r="J125" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K125" s="1">
+      <c r="K125" s="2">
         <v>0</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -11304,7 +11139,7 @@
       <c r="O125" s="1">
         <v>0</v>
       </c>
-      <c r="P125" s="1">
+      <c r="P125" s="2">
         <v>0</v>
       </c>
       <c r="Q125" s="1">
@@ -11321,7 +11156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A126" s="4">
         <v>4</v>
       </c>
@@ -11352,7 +11187,7 @@
       <c r="J126" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K126" s="1">
+      <c r="K126" s="2">
         <v>0</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -11367,7 +11202,7 @@
       <c r="O126" s="1">
         <v>0</v>
       </c>
-      <c r="P126" s="1">
+      <c r="P126" s="2">
         <v>0</v>
       </c>
       <c r="Q126" s="1">
@@ -11384,7 +11219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A127" s="4">
         <v>4</v>
       </c>
@@ -11415,7 +11250,7 @@
       <c r="J127" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K127" s="1">
+      <c r="K127" s="2">
         <v>0</v>
       </c>
       <c r="L127" s="1">
@@ -11430,7 +11265,7 @@
       <c r="O127" s="1">
         <v>0</v>
       </c>
-      <c r="P127" s="1">
+      <c r="P127" s="2">
         <v>0</v>
       </c>
       <c r="Q127" s="1">
@@ -11478,7 +11313,7 @@
       <c r="J128" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K128" s="1" t="s">
+      <c r="K128" s="2" t="s">
         <v>341</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -11493,7 +11328,7 @@
       <c r="O128" s="1">
         <v>0</v>
       </c>
-      <c r="P128" s="1">
+      <c r="P128" s="2">
         <v>0</v>
       </c>
       <c r="Q128" s="1">
@@ -11510,7 +11345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A129" s="4">
         <v>4</v>
       </c>
@@ -11541,7 +11376,7 @@
       <c r="J129" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K129" s="1">
+      <c r="K129" s="2">
         <v>0</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -11556,7 +11391,7 @@
       <c r="O129" s="1">
         <v>0</v>
       </c>
-      <c r="P129" s="1">
+      <c r="P129" s="2">
         <v>0</v>
       </c>
       <c r="Q129" s="1">
@@ -11604,7 +11439,7 @@
       <c r="J130" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K130" s="1" t="s">
+      <c r="K130" s="2" t="s">
         <v>344</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -11619,7 +11454,7 @@
       <c r="O130" s="1">
         <v>0</v>
       </c>
-      <c r="P130" s="1">
+      <c r="P130" s="2">
         <v>0</v>
       </c>
       <c r="Q130" s="1">
@@ -11667,7 +11502,7 @@
       <c r="J131" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K131" s="1" t="s">
+      <c r="K131" s="2" t="s">
         <v>346</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -11682,7 +11517,7 @@
       <c r="O131" s="1">
         <v>0</v>
       </c>
-      <c r="P131" s="1">
+      <c r="P131" s="2">
         <v>0</v>
       </c>
       <c r="Q131" s="1">
@@ -11730,7 +11565,7 @@
       <c r="J132" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K132" s="1" t="s">
+      <c r="K132" s="2" t="s">
         <v>349</v>
       </c>
       <c r="L132" s="1">
@@ -11745,7 +11580,7 @@
       <c r="O132" s="1">
         <v>0</v>
       </c>
-      <c r="P132" s="1">
+      <c r="P132" s="2">
         <v>0</v>
       </c>
       <c r="Q132" s="1">
@@ -11793,7 +11628,7 @@
       <c r="J133" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K133" s="1" t="s">
+      <c r="K133" s="2" t="s">
         <v>351</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -11808,7 +11643,7 @@
       <c r="O133" s="1">
         <v>0</v>
       </c>
-      <c r="P133" s="1">
+      <c r="P133" s="2">
         <v>0</v>
       </c>
       <c r="Q133" s="1">
@@ -11856,7 +11691,7 @@
       <c r="J134" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K134" s="1" t="s">
+      <c r="K134" s="2" t="s">
         <v>353</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -11871,7 +11706,7 @@
       <c r="O134" s="1">
         <v>0</v>
       </c>
-      <c r="P134" s="1">
+      <c r="P134" s="2">
         <v>0</v>
       </c>
       <c r="Q134" s="1">
@@ -11888,7 +11723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A135" s="4">
         <v>4</v>
       </c>
@@ -11919,7 +11754,7 @@
       <c r="J135" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K135" s="1">
+      <c r="K135" s="2">
         <v>0</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -11934,7 +11769,7 @@
       <c r="O135" s="1">
         <v>0</v>
       </c>
-      <c r="P135" s="1">
+      <c r="P135" s="2">
         <v>0</v>
       </c>
       <c r="Q135" s="1">
@@ -11982,7 +11817,7 @@
       <c r="J136" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K136" s="1" t="s">
+      <c r="K136" s="2" t="s">
         <v>356</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -11997,7 +11832,7 @@
       <c r="O136" s="1">
         <v>0</v>
       </c>
-      <c r="P136" s="1">
+      <c r="P136" s="2">
         <v>0</v>
       </c>
       <c r="Q136" s="1">
@@ -12014,7 +11849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A137" s="4">
         <v>4</v>
       </c>
@@ -12045,7 +11880,7 @@
       <c r="J137" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K137" s="1">
+      <c r="K137" s="2">
         <v>0</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -12060,7 +11895,7 @@
       <c r="O137" s="1">
         <v>0</v>
       </c>
-      <c r="P137" s="1">
+      <c r="P137" s="2">
         <v>0</v>
       </c>
       <c r="Q137" s="1">
@@ -12077,7 +11912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A138" s="4">
         <v>4</v>
       </c>
@@ -12108,7 +11943,7 @@
       <c r="J138" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K138" s="1">
+      <c r="K138" s="2">
         <v>0</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -12123,7 +11958,7 @@
       <c r="O138" s="1">
         <v>0</v>
       </c>
-      <c r="P138" s="1">
+      <c r="P138" s="2">
         <v>0</v>
       </c>
       <c r="Q138" s="1">
@@ -12140,7 +11975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A139" s="4">
         <v>4</v>
       </c>
@@ -12171,7 +12006,7 @@
       <c r="J139" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K139" s="1">
+      <c r="K139" s="2">
         <v>0</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -12186,7 +12021,7 @@
       <c r="O139" s="1">
         <v>0</v>
       </c>
-      <c r="P139" s="1">
+      <c r="P139" s="2">
         <v>0</v>
       </c>
       <c r="Q139" s="1">
@@ -12234,7 +12069,7 @@
       <c r="J140" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K140" s="1" t="s">
+      <c r="K140" s="2" t="s">
         <v>364</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -12249,7 +12084,7 @@
       <c r="O140" s="1">
         <v>0</v>
       </c>
-      <c r="P140" s="1">
+      <c r="P140" s="2">
         <v>0</v>
       </c>
       <c r="Q140" s="1">
@@ -12266,7 +12101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A141" s="4">
         <v>4</v>
       </c>
@@ -12297,7 +12132,7 @@
       <c r="J141" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K141" s="1">
+      <c r="K141" s="2">
         <v>0</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -12312,7 +12147,7 @@
       <c r="O141" s="1">
         <v>0</v>
       </c>
-      <c r="P141" s="1">
+      <c r="P141" s="2">
         <v>0</v>
       </c>
       <c r="Q141" s="1">
@@ -12329,7 +12164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A142" s="4">
         <v>4</v>
       </c>
@@ -12360,7 +12195,7 @@
       <c r="J142" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K142" s="1">
+      <c r="K142" s="2">
         <v>0</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -12375,7 +12210,7 @@
       <c r="O142" s="1">
         <v>0</v>
       </c>
-      <c r="P142" s="1">
+      <c r="P142" s="2">
         <v>0</v>
       </c>
       <c r="Q142" s="1">
@@ -12423,7 +12258,7 @@
       <c r="J143" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K143" s="1" t="s">
+      <c r="K143" s="2" t="s">
         <v>370</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -12438,7 +12273,7 @@
       <c r="O143" s="1">
         <v>0</v>
       </c>
-      <c r="P143" s="1" t="s">
+      <c r="P143" s="2" t="s">
         <v>372</v>
       </c>
       <c r="Q143" s="1">
@@ -12486,7 +12321,7 @@
       <c r="J144" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="K144" s="1" t="s">
+      <c r="K144" s="2" t="s">
         <v>375</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -12501,7 +12336,7 @@
       <c r="O144" s="1">
         <v>0</v>
       </c>
-      <c r="P144" s="1" t="s">
+      <c r="P144" s="2" t="s">
         <v>46</v>
       </c>
       <c r="Q144" s="1">
@@ -12549,7 +12384,7 @@
       <c r="J145" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="K145" s="1" t="s">
+      <c r="K145" s="2" t="s">
         <v>377</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -12564,7 +12399,7 @@
       <c r="O145" s="1">
         <v>0</v>
       </c>
-      <c r="P145" s="1">
+      <c r="P145" s="2">
         <v>8</v>
       </c>
       <c r="Q145" s="1">
@@ -12581,7 +12416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A146" s="4">
         <v>5</v>
       </c>
@@ -12612,7 +12447,7 @@
       <c r="J146" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="K146" s="1">
+      <c r="K146" s="2">
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
@@ -12627,7 +12462,7 @@
       <c r="O146" s="1">
         <v>0</v>
       </c>
-      <c r="P146" s="1">
+      <c r="P146" s="2">
         <v>8</v>
       </c>
       <c r="Q146" s="1">
@@ -12675,7 +12510,7 @@
       <c r="J147" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K147" s="1" t="s">
+      <c r="K147" s="7" t="s">
         <v>381</v>
       </c>
       <c r="L147" s="1" t="s">
@@ -12690,7 +12525,7 @@
       <c r="O147" s="1">
         <v>0</v>
       </c>
-      <c r="P147" s="1" t="s">
+      <c r="P147" s="2" t="s">
         <v>383</v>
       </c>
       <c r="Q147" s="1">
@@ -12738,7 +12573,7 @@
       <c r="J148" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K148" s="1" t="s">
+      <c r="K148" s="3" t="s">
         <v>385</v>
       </c>
       <c r="L148" s="1" t="s">
@@ -12753,7 +12588,7 @@
       <c r="O148" s="1">
         <v>0</v>
       </c>
-      <c r="P148" s="1" t="s">
+      <c r="P148" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q148" s="1">
@@ -12801,7 +12636,7 @@
       <c r="J149" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K149" s="1" t="s">
+      <c r="K149" s="2" t="s">
         <v>388</v>
       </c>
       <c r="L149" s="1" t="s">
@@ -12816,7 +12651,7 @@
       <c r="O149" s="1">
         <v>0</v>
       </c>
-      <c r="P149" s="1" t="s">
+      <c r="P149" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q149" s="1">
@@ -12864,7 +12699,7 @@
       <c r="J150" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K150" s="1" t="s">
+      <c r="K150" s="2" t="s">
         <v>391</v>
       </c>
       <c r="L150" s="1" t="s">
@@ -12879,7 +12714,7 @@
       <c r="O150" s="1">
         <v>0</v>
       </c>
-      <c r="P150" s="1" t="s">
+      <c r="P150" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q150" s="1">
@@ -12927,7 +12762,7 @@
       <c r="J151" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K151" s="1" t="s">
+      <c r="K151" s="2" t="s">
         <v>393</v>
       </c>
       <c r="L151" s="1" t="s">
@@ -12942,7 +12777,7 @@
       <c r="O151" s="1">
         <v>0</v>
       </c>
-      <c r="P151" s="1" t="s">
+      <c r="P151" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q151" s="1">
@@ -12990,7 +12825,7 @@
       <c r="J152" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K152" s="1" t="s">
+      <c r="K152" s="2" t="s">
         <v>396</v>
       </c>
       <c r="L152" s="1">
@@ -13005,7 +12840,7 @@
       <c r="O152" s="1">
         <v>0</v>
       </c>
-      <c r="P152" s="1" t="s">
+      <c r="P152" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q152" s="1">
@@ -13022,7 +12857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A153" s="4">
         <v>6</v>
       </c>
@@ -13053,7 +12888,7 @@
       <c r="J153" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K153" s="1">
+      <c r="K153" s="2">
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
@@ -13068,7 +12903,7 @@
       <c r="O153" s="1">
         <v>0</v>
       </c>
-      <c r="P153" s="1" t="s">
+      <c r="P153" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q153" s="1">
@@ -13116,7 +12951,7 @@
       <c r="J154" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K154" s="1" t="s">
+      <c r="K154" s="2" t="s">
         <v>398</v>
       </c>
       <c r="L154" s="1" t="s">
@@ -13131,7 +12966,7 @@
       <c r="O154" s="1">
         <v>0</v>
       </c>
-      <c r="P154" s="1" t="s">
+      <c r="P154" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q154" s="1">
@@ -13179,7 +13014,7 @@
       <c r="J155" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K155" s="1" t="s">
+      <c r="K155" s="2" t="s">
         <v>400</v>
       </c>
       <c r="L155" s="1">
@@ -13194,7 +13029,7 @@
       <c r="O155" s="1">
         <v>0</v>
       </c>
-      <c r="P155" s="1" t="s">
+      <c r="P155" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q155" s="1">
@@ -13242,7 +13077,7 @@
       <c r="J156" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K156" s="1" t="s">
+      <c r="K156" s="2" t="s">
         <v>401</v>
       </c>
       <c r="L156" s="1" t="s">
@@ -13257,7 +13092,7 @@
       <c r="O156" s="1">
         <v>0</v>
       </c>
-      <c r="P156" s="1" t="s">
+      <c r="P156" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q156" s="1">
@@ -13305,7 +13140,7 @@
       <c r="J157" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K157" s="1" t="s">
+      <c r="K157" s="2" t="s">
         <v>404</v>
       </c>
       <c r="L157" s="1" t="s">
@@ -13320,7 +13155,7 @@
       <c r="O157" s="1">
         <v>0</v>
       </c>
-      <c r="P157" s="1" t="s">
+      <c r="P157" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q157" s="1">
@@ -13368,7 +13203,7 @@
       <c r="J158" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K158" s="1" t="s">
+      <c r="K158" s="2" t="s">
         <v>406</v>
       </c>
       <c r="L158" s="1" t="s">
@@ -13383,7 +13218,7 @@
       <c r="O158" s="1">
         <v>0</v>
       </c>
-      <c r="P158" s="1" t="s">
+      <c r="P158" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q158" s="1">
@@ -13431,7 +13266,7 @@
       <c r="J159" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K159" s="1" t="s">
+      <c r="K159" s="2" t="s">
         <v>409</v>
       </c>
       <c r="L159" s="1" t="s">
@@ -13446,7 +13281,7 @@
       <c r="O159" s="1">
         <v>0</v>
       </c>
-      <c r="P159" s="1" t="s">
+      <c r="P159" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q159" s="1">
@@ -13494,7 +13329,7 @@
       <c r="J160" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K160" s="1" t="s">
+      <c r="K160" s="2" t="s">
         <v>411</v>
       </c>
       <c r="L160" s="1" t="s">
@@ -13509,7 +13344,7 @@
       <c r="O160" s="1">
         <v>0</v>
       </c>
-      <c r="P160" s="1" t="s">
+      <c r="P160" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q160" s="1">
@@ -13526,7 +13361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A161" s="4">
         <v>6</v>
       </c>
@@ -13557,7 +13392,7 @@
       <c r="J161" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K161" s="1">
+      <c r="K161" s="2">
         <v>0</v>
       </c>
       <c r="L161" s="1">
@@ -13572,7 +13407,7 @@
       <c r="O161" s="1">
         <v>0</v>
       </c>
-      <c r="P161" s="1" t="s">
+      <c r="P161" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q161" s="1">
@@ -13620,7 +13455,7 @@
       <c r="J162" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K162" s="1" t="s">
+      <c r="K162" s="2" t="s">
         <v>413</v>
       </c>
       <c r="L162" s="1" t="s">
@@ -13635,7 +13470,7 @@
       <c r="O162" s="1">
         <v>0</v>
       </c>
-      <c r="P162" s="1" t="s">
+      <c r="P162" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q162" s="1">
@@ -13652,7 +13487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A163" s="4">
         <v>6</v>
       </c>
@@ -13683,7 +13518,7 @@
       <c r="J163" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K163" s="1">
+      <c r="K163" s="2">
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
@@ -13698,7 +13533,7 @@
       <c r="O163" s="1">
         <v>0</v>
       </c>
-      <c r="P163" s="1" t="s">
+      <c r="P163" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q163" s="1">
@@ -13746,7 +13581,7 @@
       <c r="J164" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K164" s="2" t="s">
         <v>416</v>
       </c>
       <c r="L164" s="1">
@@ -13761,7 +13596,7 @@
       <c r="O164" s="1">
         <v>0</v>
       </c>
-      <c r="P164" s="1" t="s">
+      <c r="P164" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q164" s="1">
@@ -13809,7 +13644,7 @@
       <c r="J165" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K165" s="1" t="s">
+      <c r="K165" s="2" t="s">
         <v>418</v>
       </c>
       <c r="L165" s="1" t="s">
@@ -13824,7 +13659,7 @@
       <c r="O165" s="1">
         <v>0</v>
       </c>
-      <c r="P165" s="1" t="s">
+      <c r="P165" s="2" t="s">
         <v>387</v>
       </c>
       <c r="Q165" s="1">
@@ -13841,7 +13676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A166" s="4">
         <v>6</v>
       </c>
@@ -13872,7 +13707,7 @@
       <c r="J166" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K166" s="1">
+      <c r="K166" s="2">
         <v>0</v>
       </c>
       <c r="L166" s="1">
@@ -13887,7 +13722,7 @@
       <c r="O166" s="1">
         <v>0</v>
       </c>
-      <c r="P166" s="1" t="s">
+      <c r="P166" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q166" s="1">
@@ -13935,7 +13770,7 @@
       <c r="J167" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K167" s="1" t="s">
+      <c r="K167" s="2" t="s">
         <v>421</v>
       </c>
       <c r="L167" s="1" t="s">
@@ -13950,7 +13785,7 @@
       <c r="O167" s="1">
         <v>0</v>
       </c>
-      <c r="P167" s="1" t="s">
+      <c r="P167" s="2" t="s">
         <v>199</v>
       </c>
       <c r="Q167" s="1">
@@ -13998,7 +13833,7 @@
       <c r="J168" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K168" s="1" t="s">
+      <c r="K168" s="2" t="s">
         <v>423</v>
       </c>
       <c r="L168" s="1" t="s">
@@ -14013,7 +13848,7 @@
       <c r="O168" s="1">
         <v>0</v>
       </c>
-      <c r="P168" s="1" t="s">
+      <c r="P168" s="2" t="s">
         <v>425</v>
       </c>
       <c r="Q168" s="1">
@@ -14030,7 +13865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A169" s="4">
         <v>6</v>
       </c>
@@ -14061,7 +13896,7 @@
       <c r="J169" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K169" s="1">
+      <c r="K169" s="2">
         <v>0</v>
       </c>
       <c r="L169" s="1" t="s">
@@ -14076,7 +13911,7 @@
       <c r="O169" s="1">
         <v>0</v>
       </c>
-      <c r="P169" s="1" t="s">
+      <c r="P169" s="2" t="s">
         <v>46</v>
       </c>
       <c r="Q169" s="1">
@@ -14124,7 +13959,7 @@
       <c r="J170" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K170" s="1" t="s">
+      <c r="K170" s="2" t="s">
         <v>428</v>
       </c>
       <c r="L170" s="1">
@@ -14139,7 +13974,7 @@
       <c r="O170" s="1">
         <v>0</v>
       </c>
-      <c r="P170" s="1" t="s">
+      <c r="P170" s="2" t="s">
         <v>429</v>
       </c>
       <c r="Q170" s="1">
@@ -14187,7 +14022,7 @@
       <c r="J171" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="K171" s="1" t="s">
+      <c r="K171" s="2" t="s">
         <v>431</v>
       </c>
       <c r="L171" s="1" t="s">
@@ -14202,7 +14037,7 @@
       <c r="O171" s="1">
         <v>0</v>
       </c>
-      <c r="P171" s="1" t="s">
+      <c r="P171" s="2" t="s">
         <v>433</v>
       </c>
       <c r="Q171" s="1">
@@ -14250,7 +14085,7 @@
       <c r="J172" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="K172" s="1" t="s">
+      <c r="K172" s="2" t="s">
         <v>434</v>
       </c>
       <c r="L172" s="1">
@@ -14265,7 +14100,7 @@
       <c r="O172" s="1">
         <v>0</v>
       </c>
-      <c r="P172" s="1" t="s">
+      <c r="P172" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q172" s="1">
@@ -14313,7 +14148,7 @@
       <c r="J173" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="K173" s="1" t="s">
+      <c r="K173" s="2" t="s">
         <v>436</v>
       </c>
       <c r="L173" s="1" t="s">
@@ -14328,7 +14163,7 @@
       <c r="O173" s="1">
         <v>0</v>
       </c>
-      <c r="P173" s="1" t="s">
+      <c r="P173" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q173" s="1">
@@ -14376,7 +14211,7 @@
       <c r="J174" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="K174" s="1" t="s">
+      <c r="K174" s="2" t="s">
         <v>439</v>
       </c>
       <c r="L174" s="1" t="s">
@@ -14391,7 +14226,7 @@
       <c r="O174" s="1">
         <v>0</v>
       </c>
-      <c r="P174" s="1" t="s">
+      <c r="P174" s="2" t="s">
         <v>442</v>
       </c>
       <c r="Q174" s="1">
@@ -14439,7 +14274,7 @@
       <c r="J175" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="K175" s="1" t="s">
+      <c r="K175" s="2" t="s">
         <v>444</v>
       </c>
       <c r="L175" s="1">
@@ -14454,7 +14289,7 @@
       <c r="O175" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="P175" s="1" t="s">
+      <c r="P175" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q175" s="1">
@@ -14471,7 +14306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A176" s="4">
         <v>6</v>
       </c>
@@ -14502,7 +14337,7 @@
       <c r="J176" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="K176" s="1">
+      <c r="K176" s="2">
         <v>0</v>
       </c>
       <c r="L176" s="1">
@@ -14517,7 +14352,7 @@
       <c r="O176" s="1">
         <v>0</v>
       </c>
-      <c r="P176" s="1" t="s">
+      <c r="P176" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q176" s="1">
@@ -14534,7 +14369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A177" s="4">
         <v>6</v>
       </c>
@@ -14565,7 +14400,7 @@
       <c r="J177" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="K177" s="1" t="s">
+      <c r="K177" s="2" t="s">
         <v>450</v>
       </c>
       <c r="L177" s="1" t="s">
@@ -14580,7 +14415,7 @@
       <c r="O177" s="1">
         <v>0</v>
       </c>
-      <c r="P177" s="1" t="s">
+      <c r="P177" s="2" t="s">
         <v>311</v>
       </c>
       <c r="Q177" s="1">
@@ -14597,7 +14432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A178" s="4">
         <v>6</v>
       </c>
@@ -14628,7 +14463,7 @@
       <c r="J178" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="K178" s="1" t="s">
+      <c r="K178" s="2" t="s">
         <v>454</v>
       </c>
       <c r="L178" s="1">
@@ -14643,7 +14478,7 @@
       <c r="O178" s="1">
         <v>0</v>
       </c>
-      <c r="P178" s="1" t="s">
+      <c r="P178" s="2" t="s">
         <v>455</v>
       </c>
       <c r="Q178" s="1">
@@ -14660,7 +14495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A179" s="4">
         <v>7</v>
       </c>
@@ -14691,7 +14526,7 @@
       <c r="J179" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K179" s="1" t="s">
+      <c r="K179" s="2" t="s">
         <v>458</v>
       </c>
       <c r="L179" s="1" t="s">
@@ -14706,7 +14541,7 @@
       <c r="O179" s="1">
         <v>0</v>
       </c>
-      <c r="P179" s="1" t="s">
+      <c r="P179" s="2" t="s">
         <v>460</v>
       </c>
       <c r="Q179" s="1">
@@ -14723,7 +14558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A180" s="4">
         <v>7</v>
       </c>
@@ -14754,7 +14589,7 @@
       <c r="J180" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K180" s="1">
+      <c r="K180" s="2">
         <v>0</v>
       </c>
       <c r="L180" s="1" t="s">
@@ -14769,7 +14604,7 @@
       <c r="O180" s="1">
         <v>0</v>
       </c>
-      <c r="P180" s="1">
+      <c r="P180" s="2">
         <v>1</v>
       </c>
       <c r="Q180" s="1">
@@ -14786,7 +14621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A181" s="4">
         <v>7</v>
       </c>
@@ -14817,7 +14652,7 @@
       <c r="J181" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K181" s="1">
+      <c r="K181" s="2">
         <v>0</v>
       </c>
       <c r="L181" s="1" t="s">
@@ -14832,7 +14667,7 @@
       <c r="O181" s="1">
         <v>0</v>
       </c>
-      <c r="P181" s="1">
+      <c r="P181" s="2">
         <v>1</v>
       </c>
       <c r="Q181" s="1">
@@ -14848,9 +14683,8 @@
       <c r="T181" s="1">
         <v>0</v>
       </c>
-      <c r="U181" s="7"/>
-    </row>
-    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A182" s="4">
         <v>7</v>
       </c>
@@ -14881,7 +14715,7 @@
       <c r="J182" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K182" s="1">
+      <c r="K182" s="2">
         <v>0</v>
       </c>
       <c r="L182" s="1" t="s">
@@ -14896,7 +14730,7 @@
       <c r="O182" s="1">
         <v>0</v>
       </c>
-      <c r="P182" s="1">
+      <c r="P182" s="2">
         <v>1</v>
       </c>
       <c r="Q182" s="1">
@@ -14912,9 +14746,8 @@
       <c r="T182" s="1">
         <v>0</v>
       </c>
-      <c r="U182" s="7"/>
-    </row>
-    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A183" s="4">
         <v>7</v>
       </c>
@@ -14945,7 +14778,7 @@
       <c r="J183" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K183" s="1">
+      <c r="K183" s="2">
         <v>0</v>
       </c>
       <c r="L183" s="1" t="s">
@@ -14960,7 +14793,7 @@
       <c r="O183" s="1">
         <v>0</v>
       </c>
-      <c r="P183" s="1">
+      <c r="P183" s="2">
         <v>1</v>
       </c>
       <c r="Q183" s="1">
@@ -14976,9 +14809,8 @@
       <c r="T183" s="1">
         <v>0</v>
       </c>
-      <c r="U183" s="7"/>
-    </row>
-    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A184" s="4">
         <v>7</v>
       </c>
@@ -15009,7 +14841,7 @@
       <c r="J184" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K184" s="1">
+      <c r="K184" s="2">
         <v>0</v>
       </c>
       <c r="L184" s="1" t="s">
@@ -15024,7 +14856,7 @@
       <c r="O184" s="1">
         <v>0</v>
       </c>
-      <c r="P184" s="1">
+      <c r="P184" s="2">
         <v>1</v>
       </c>
       <c r="Q184" s="1">
@@ -15040,9 +14872,8 @@
       <c r="T184" s="1">
         <v>0</v>
       </c>
-      <c r="U184" s="7"/>
-    </row>
-    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A185" s="4">
         <v>7</v>
       </c>
@@ -15073,7 +14904,7 @@
       <c r="J185" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K185" s="1">
+      <c r="K185" s="2">
         <v>0</v>
       </c>
       <c r="L185" s="1" t="s">
@@ -15088,7 +14919,7 @@
       <c r="O185" s="1">
         <v>0</v>
       </c>
-      <c r="P185" s="1">
+      <c r="P185" s="2">
         <v>1</v>
       </c>
       <c r="Q185" s="1">
@@ -15104,9 +14935,8 @@
       <c r="T185" s="1">
         <v>0</v>
       </c>
-      <c r="U185" s="7"/>
-    </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.4">
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A186" s="4">
         <v>7</v>
       </c>
@@ -15137,7 +14967,7 @@
       <c r="J186" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K186" s="1" t="s">
+      <c r="K186" s="2" t="s">
         <v>471</v>
       </c>
       <c r="L186" s="1" t="s">
@@ -15152,7 +14982,7 @@
       <c r="O186" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="P186" s="1">
+      <c r="P186" s="2">
         <v>1</v>
       </c>
       <c r="Q186" s="1">
@@ -15168,9 +14998,8 @@
       <c r="T186" s="1">
         <v>0</v>
       </c>
-      <c r="U186" s="7"/>
-    </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.4">
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A187" s="4">
         <v>7</v>
       </c>
@@ -15201,7 +15030,7 @@
       <c r="J187" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K187" s="1" t="s">
+      <c r="K187" s="2" t="s">
         <v>476</v>
       </c>
       <c r="L187" s="1">
@@ -15216,7 +15045,7 @@
       <c r="O187" s="1">
         <v>0</v>
       </c>
-      <c r="P187" s="1">
+      <c r="P187" s="2">
         <v>1</v>
       </c>
       <c r="Q187" s="1">
@@ -15232,9 +15061,8 @@
       <c r="T187" s="1">
         <v>0</v>
       </c>
-      <c r="U187" s="7"/>
-    </row>
-    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A188" s="4">
         <v>7</v>
       </c>
@@ -15265,7 +15093,7 @@
       <c r="J188" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K188" s="1">
+      <c r="K188" s="2">
         <v>0</v>
       </c>
       <c r="L188" s="1" t="s">
@@ -15280,7 +15108,7 @@
       <c r="O188" s="1">
         <v>0</v>
       </c>
-      <c r="P188" s="1">
+      <c r="P188" s="2">
         <v>1</v>
       </c>
       <c r="Q188" s="1">
@@ -15296,9 +15124,8 @@
       <c r="T188" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U188" s="7"/>
-    </row>
-    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A189" s="4">
         <v>7</v>
       </c>
@@ -15329,7 +15156,7 @@
       <c r="J189" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K189" s="1">
+      <c r="K189" s="2">
         <v>0</v>
       </c>
       <c r="L189" s="1" t="s">
@@ -15344,7 +15171,7 @@
       <c r="O189" s="1">
         <v>0</v>
       </c>
-      <c r="P189" s="1">
+      <c r="P189" s="2">
         <v>1</v>
       </c>
       <c r="Q189" s="1">
@@ -15360,9 +15187,8 @@
       <c r="T189" s="1">
         <v>0</v>
       </c>
-      <c r="U189" s="7"/>
-    </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.4">
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A190" s="4">
         <v>7</v>
       </c>
@@ -15393,7 +15219,7 @@
       <c r="J190" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K190" s="1" t="s">
+      <c r="K190" s="2" t="s">
         <v>483</v>
       </c>
       <c r="L190" s="1" t="s">
@@ -15408,7 +15234,7 @@
       <c r="O190" s="1">
         <v>0</v>
       </c>
-      <c r="P190" s="1">
+      <c r="P190" s="2">
         <v>1</v>
       </c>
       <c r="Q190" s="1">
@@ -15424,9 +15250,8 @@
       <c r="T190" s="1">
         <v>0</v>
       </c>
-      <c r="U190" s="7"/>
-    </row>
-    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A191" s="4">
         <v>7</v>
       </c>
@@ -15457,7 +15282,7 @@
       <c r="J191" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K191" s="1">
+      <c r="K191" s="2">
         <v>0</v>
       </c>
       <c r="L191" s="1" t="s">
@@ -15472,7 +15297,7 @@
       <c r="O191" s="1">
         <v>0</v>
       </c>
-      <c r="P191" s="1">
+      <c r="P191" s="2">
         <v>1</v>
       </c>
       <c r="Q191" s="1">
@@ -15488,9 +15313,8 @@
       <c r="T191" s="1">
         <v>0</v>
       </c>
-      <c r="U191" s="7"/>
-    </row>
-    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A192" s="4">
         <v>7</v>
       </c>
@@ -15521,7 +15345,7 @@
       <c r="J192" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K192" s="1">
+      <c r="K192" s="2">
         <v>0</v>
       </c>
       <c r="L192" s="1" t="s">
@@ -15536,7 +15360,7 @@
       <c r="O192" s="1">
         <v>0</v>
       </c>
-      <c r="P192" s="1">
+      <c r="P192" s="2">
         <v>1</v>
       </c>
       <c r="Q192" s="1">
@@ -15552,7 +15376,6 @@
       <c r="T192" s="1">
         <v>0</v>
       </c>
-      <c r="U192" s="7"/>
     </row>
     <row r="193" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A193" s="4">
@@ -15585,7 +15408,7 @@
       <c r="J193" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K193" s="1" t="s">
+      <c r="K193" s="2" t="s">
         <v>490</v>
       </c>
       <c r="L193" s="1" t="s">
@@ -15600,7 +15423,7 @@
       <c r="O193" s="1">
         <v>0</v>
       </c>
-      <c r="P193" s="1" t="s">
+      <c r="P193" s="2" t="s">
         <v>493</v>
       </c>
       <c r="Q193" s="1">
@@ -15617,7 +15440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A194" s="4">
         <v>7</v>
       </c>
@@ -15648,7 +15471,7 @@
       <c r="J194" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K194" s="1">
+      <c r="K194" s="2">
         <v>0</v>
       </c>
       <c r="L194" s="1" t="s">
@@ -15663,7 +15486,7 @@
       <c r="O194" s="1">
         <v>0</v>
       </c>
-      <c r="P194" s="1" t="s">
+      <c r="P194" s="2" t="s">
         <v>496</v>
       </c>
       <c r="Q194" s="1">
@@ -15711,7 +15534,7 @@
       <c r="J195" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K195" s="1" t="s">
+      <c r="K195" s="2" t="s">
         <v>497</v>
       </c>
       <c r="L195" s="1">
@@ -15726,7 +15549,7 @@
       <c r="O195" s="1">
         <v>0</v>
       </c>
-      <c r="P195" s="1" t="s">
+      <c r="P195" s="2" t="s">
         <v>499</v>
       </c>
       <c r="Q195" s="1">
@@ -15774,7 +15597,7 @@
       <c r="J196" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K196" s="1" t="s">
+      <c r="K196" s="2" t="s">
         <v>500</v>
       </c>
       <c r="L196" s="1">
@@ -15789,7 +15612,7 @@
       <c r="O196" s="1">
         <v>0</v>
       </c>
-      <c r="P196" s="1" t="s">
+      <c r="P196" s="2" t="s">
         <v>499</v>
       </c>
       <c r="Q196" s="1">
@@ -15837,7 +15660,7 @@
       <c r="J197" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K197" s="1" t="s">
+      <c r="K197" s="2" t="s">
         <v>502</v>
       </c>
       <c r="L197" s="1" t="s">
@@ -15852,7 +15675,7 @@
       <c r="O197" s="1">
         <v>0</v>
       </c>
-      <c r="P197" s="1" t="s">
+      <c r="P197" s="2" t="s">
         <v>505</v>
       </c>
       <c r="Q197" s="1">
@@ -15869,7 +15692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A198" s="4">
         <v>7</v>
       </c>
@@ -15900,7 +15723,7 @@
       <c r="J198" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K198" s="1">
+      <c r="K198" s="2">
         <v>0</v>
       </c>
       <c r="L198" s="1" t="s">
@@ -15915,7 +15738,7 @@
       <c r="O198" s="1">
         <v>0</v>
       </c>
-      <c r="P198" s="1">
+      <c r="P198" s="2">
         <v>1</v>
       </c>
       <c r="Q198" s="1">
@@ -15932,7 +15755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A199" s="4">
         <v>7</v>
       </c>
@@ -15963,7 +15786,7 @@
       <c r="J199" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K199" s="1">
+      <c r="K199" s="2">
         <v>0</v>
       </c>
       <c r="L199" s="1" t="s">
@@ -15978,7 +15801,7 @@
       <c r="O199" s="1">
         <v>0</v>
       </c>
-      <c r="P199" s="1">
+      <c r="P199" s="2">
         <v>1</v>
       </c>
       <c r="Q199" s="1">
@@ -15995,7 +15818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A200" s="4">
         <v>7</v>
       </c>
@@ -16026,7 +15849,7 @@
       <c r="J200" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K200" s="1">
+      <c r="K200" s="2">
         <v>0</v>
       </c>
       <c r="L200" s="1" t="s">
@@ -16041,7 +15864,7 @@
       <c r="O200" s="1">
         <v>0</v>
       </c>
-      <c r="P200" s="1">
+      <c r="P200" s="2">
         <v>1</v>
       </c>
       <c r="Q200" s="1">
@@ -16058,7 +15881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A201" s="4">
         <v>7</v>
       </c>
@@ -16089,7 +15912,7 @@
       <c r="J201" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K201" s="1">
+      <c r="K201" s="2">
         <v>0</v>
       </c>
       <c r="L201" s="1" t="s">
@@ -16104,7 +15927,7 @@
       <c r="O201" s="1">
         <v>0</v>
       </c>
-      <c r="P201" s="1">
+      <c r="P201" s="2">
         <v>1</v>
       </c>
       <c r="Q201" s="1">
@@ -16121,7 +15944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A202" s="4">
         <v>7</v>
       </c>
@@ -16152,7 +15975,7 @@
       <c r="J202" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K202" s="1">
+      <c r="K202" s="2">
         <v>0</v>
       </c>
       <c r="L202" s="1" t="s">
@@ -16167,7 +15990,7 @@
       <c r="O202" s="1">
         <v>0</v>
       </c>
-      <c r="P202" s="1">
+      <c r="P202" s="2">
         <v>1</v>
       </c>
       <c r="Q202" s="1">
@@ -16184,7 +16007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A203" s="4">
         <v>7</v>
       </c>
@@ -16215,7 +16038,7 @@
       <c r="J203" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K203" s="1">
+      <c r="K203" s="2">
         <v>0</v>
       </c>
       <c r="L203" s="1" t="s">
@@ -16230,7 +16053,7 @@
       <c r="O203" s="1">
         <v>0</v>
       </c>
-      <c r="P203" s="1">
+      <c r="P203" s="2">
         <v>1</v>
       </c>
       <c r="Q203" s="1">
@@ -16247,7 +16070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A204" s="4">
         <v>7</v>
       </c>
@@ -16278,7 +16101,7 @@
       <c r="J204" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K204" s="1">
+      <c r="K204" s="2">
         <v>0</v>
       </c>
       <c r="L204" s="1" t="s">
@@ -16293,7 +16116,7 @@
       <c r="O204" s="1">
         <v>0</v>
       </c>
-      <c r="P204" s="1">
+      <c r="P204" s="2">
         <v>1</v>
       </c>
       <c r="Q204" s="1">
@@ -16341,7 +16164,7 @@
       <c r="J205" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K205" s="1" t="s">
+      <c r="K205" s="2" t="s">
         <v>521</v>
       </c>
       <c r="L205" s="1">
@@ -16356,7 +16179,7 @@
       <c r="O205" s="1">
         <v>0</v>
       </c>
-      <c r="P205" s="1">
+      <c r="P205" s="2">
         <v>2</v>
       </c>
       <c r="Q205" s="1">
@@ -16373,7 +16196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A206" s="4">
         <v>8</v>
       </c>
@@ -16404,7 +16227,7 @@
       <c r="J206" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K206" s="1">
+      <c r="K206" s="2">
         <v>0</v>
       </c>
       <c r="L206" s="1" t="s">
@@ -16419,7 +16242,7 @@
       <c r="O206" s="1">
         <v>0</v>
       </c>
-      <c r="P206" s="1">
+      <c r="P206" s="2">
         <v>2</v>
       </c>
       <c r="Q206" s="1">
@@ -16467,7 +16290,7 @@
       <c r="J207" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K207" s="1" t="s">
+      <c r="K207" s="2" t="s">
         <v>525</v>
       </c>
       <c r="L207" s="1" t="s">
@@ -16482,7 +16305,7 @@
       <c r="O207" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="P207" s="1">
+      <c r="P207" s="2">
         <v>2</v>
       </c>
       <c r="Q207" s="1">
@@ -16499,7 +16322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A208" s="4">
         <v>8</v>
       </c>
@@ -16530,7 +16353,7 @@
       <c r="J208" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K208" s="1">
+      <c r="K208" s="2">
         <v>0</v>
       </c>
       <c r="L208" s="1" t="s">
@@ -16545,7 +16368,7 @@
       <c r="O208" s="1">
         <v>0</v>
       </c>
-      <c r="P208" s="1">
+      <c r="P208" s="2">
         <v>2</v>
       </c>
       <c r="Q208" s="1">
@@ -16562,7 +16385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A209" s="4">
         <v>8</v>
       </c>
@@ -16593,7 +16416,7 @@
       <c r="J209" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K209" s="1">
+      <c r="K209" s="2">
         <v>0</v>
       </c>
       <c r="L209" s="1" t="s">
@@ -16608,7 +16431,7 @@
       <c r="O209" s="1">
         <v>0</v>
       </c>
-      <c r="P209" s="1">
+      <c r="P209" s="2">
         <v>2</v>
       </c>
       <c r="Q209" s="1">
@@ -16625,7 +16448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A210" s="4">
         <v>8</v>
       </c>
@@ -16656,7 +16479,7 @@
       <c r="J210" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K210" s="1">
+      <c r="K210" s="2">
         <v>0</v>
       </c>
       <c r="L210" s="1" t="s">
@@ -16671,7 +16494,7 @@
       <c r="O210" s="1">
         <v>0</v>
       </c>
-      <c r="P210" s="1">
+      <c r="P210" s="2">
         <v>2</v>
       </c>
       <c r="Q210" s="1">
@@ -16688,7 +16511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A211" s="4">
         <v>8</v>
       </c>
@@ -16719,7 +16542,7 @@
       <c r="J211" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K211" s="1">
+      <c r="K211" s="2">
         <v>0</v>
       </c>
       <c r="L211" s="1" t="s">
@@ -16734,7 +16557,7 @@
       <c r="O211" s="1">
         <v>0</v>
       </c>
-      <c r="P211" s="1">
+      <c r="P211" s="2">
         <v>2</v>
       </c>
       <c r="Q211" s="1">
@@ -16751,7 +16574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A212" s="4">
         <v>8</v>
       </c>
@@ -16782,7 +16605,7 @@
       <c r="J212" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K212" s="1">
+      <c r="K212" s="2">
         <v>0</v>
       </c>
       <c r="L212" s="1" t="s">
@@ -16797,7 +16620,7 @@
       <c r="O212" s="1">
         <v>0</v>
       </c>
-      <c r="P212" s="1">
+      <c r="P212" s="2">
         <v>2</v>
       </c>
       <c r="Q212" s="1">
@@ -16845,7 +16668,7 @@
       <c r="J213" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K213" s="1" t="s">
+      <c r="K213" s="2" t="s">
         <v>538</v>
       </c>
       <c r="L213" s="1" t="s">
@@ -16860,7 +16683,7 @@
       <c r="O213" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="P213" s="1">
+      <c r="P213" s="2">
         <v>2</v>
       </c>
       <c r="Q213" s="1">
@@ -16877,7 +16700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A214" s="4">
         <v>8</v>
       </c>
@@ -16908,7 +16731,7 @@
       <c r="J214" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K214" s="1">
+      <c r="K214" s="2">
         <v>0</v>
       </c>
       <c r="L214" s="1" t="s">
@@ -16923,7 +16746,7 @@
       <c r="O214" s="1">
         <v>0</v>
       </c>
-      <c r="P214" s="1">
+      <c r="P214" s="2">
         <v>2</v>
       </c>
       <c r="Q214" s="1">
@@ -16940,7 +16763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A215" s="4">
         <v>8</v>
       </c>
@@ -16971,7 +16794,7 @@
       <c r="J215" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K215" s="1">
+      <c r="K215" s="2">
         <v>0</v>
       </c>
       <c r="L215" s="1" t="s">
@@ -16986,7 +16809,7 @@
       <c r="O215" s="1">
         <v>0</v>
       </c>
-      <c r="P215" s="1">
+      <c r="P215" s="2">
         <v>2</v>
       </c>
       <c r="Q215" s="1">
@@ -17003,7 +16826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A216" s="4">
         <v>8</v>
       </c>
@@ -17034,7 +16857,7 @@
       <c r="J216" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K216" s="1">
+      <c r="K216" s="2">
         <v>0</v>
       </c>
       <c r="L216" s="1" t="s">
@@ -17049,7 +16872,7 @@
       <c r="O216" s="1">
         <v>0</v>
       </c>
-      <c r="P216" s="1">
+      <c r="P216" s="2">
         <v>2</v>
       </c>
       <c r="Q216" s="1">
@@ -17097,7 +16920,7 @@
       <c r="J217" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K217" s="1" t="s">
+      <c r="K217" s="2" t="s">
         <v>548</v>
       </c>
       <c r="L217" s="1" t="s">
@@ -17112,7 +16935,7 @@
       <c r="O217" s="1">
         <v>0</v>
       </c>
-      <c r="P217" s="1">
+      <c r="P217" s="2">
         <v>2</v>
       </c>
       <c r="Q217" s="1">
@@ -17160,7 +16983,7 @@
       <c r="J218" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K218" s="1" t="s">
+      <c r="K218" s="2" t="s">
         <v>552</v>
       </c>
       <c r="L218" s="1" t="s">
@@ -17175,7 +16998,7 @@
       <c r="O218" s="1">
         <v>0</v>
       </c>
-      <c r="P218" s="1">
+      <c r="P218" s="2">
         <v>2</v>
       </c>
       <c r="Q218" s="1">
@@ -17223,7 +17046,7 @@
       <c r="J219" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K219" s="1" t="s">
+      <c r="K219" s="2" t="s">
         <v>555</v>
       </c>
       <c r="L219" s="1" t="s">
@@ -17238,7 +17061,7 @@
       <c r="O219" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="P219" s="1">
+      <c r="P219" s="2">
         <v>2</v>
       </c>
       <c r="Q219" s="1">
@@ -17286,7 +17109,7 @@
       <c r="J220" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K220" s="1" t="s">
+      <c r="K220" s="2" t="s">
         <v>560</v>
       </c>
       <c r="L220" s="1" t="s">
@@ -17301,7 +17124,7 @@
       <c r="O220" s="1">
         <v>0</v>
       </c>
-      <c r="P220" s="1">
+      <c r="P220" s="2">
         <v>2</v>
       </c>
       <c r="Q220" s="1">
@@ -17318,7 +17141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A221" s="4">
         <v>8</v>
       </c>
@@ -17349,7 +17172,7 @@
       <c r="J221" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K221" s="1">
+      <c r="K221" s="2">
         <v>0</v>
       </c>
       <c r="L221" s="1">
@@ -17364,7 +17187,7 @@
       <c r="O221" s="1">
         <v>0</v>
       </c>
-      <c r="P221" s="1">
+      <c r="P221" s="2">
         <v>2</v>
       </c>
       <c r="Q221" s="1">
@@ -17381,7 +17204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A222" s="4">
         <v>8</v>
       </c>
@@ -17412,7 +17235,7 @@
       <c r="J222" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K222" s="1">
+      <c r="K222" s="2">
         <v>0</v>
       </c>
       <c r="L222" s="1" t="s">
@@ -17427,7 +17250,7 @@
       <c r="O222" s="1">
         <v>0</v>
       </c>
-      <c r="P222" s="1">
+      <c r="P222" s="2">
         <v>2</v>
       </c>
       <c r="Q222" s="1">
@@ -17444,7 +17267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A223" s="4">
         <v>8</v>
       </c>
@@ -17475,7 +17298,7 @@
       <c r="J223" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K223" s="1">
+      <c r="K223" s="2">
         <v>0</v>
       </c>
       <c r="L223" s="1" t="s">
@@ -17490,7 +17313,7 @@
       <c r="O223" s="1">
         <v>0</v>
       </c>
-      <c r="P223" s="1">
+      <c r="P223" s="2">
         <v>2</v>
       </c>
       <c r="Q223" s="1">
@@ -17538,7 +17361,7 @@
       <c r="J224" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K224" s="1" t="s">
+      <c r="K224" s="2" t="s">
         <v>568</v>
       </c>
       <c r="L224" s="1">
@@ -17553,7 +17376,7 @@
       <c r="O224" s="1">
         <v>0</v>
       </c>
-      <c r="P224" s="1">
+      <c r="P224" s="2">
         <v>2</v>
       </c>
       <c r="Q224" s="1">
@@ -17570,7 +17393,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="225" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A225" s="4">
         <v>8</v>
       </c>
@@ -17601,7 +17424,7 @@
       <c r="J225" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K225" s="1">
+      <c r="K225" s="2">
         <v>0</v>
       </c>
       <c r="L225" s="1" t="s">
@@ -17616,7 +17439,7 @@
       <c r="O225" s="1">
         <v>0</v>
       </c>
-      <c r="P225" s="1">
+      <c r="P225" s="2">
         <v>2</v>
       </c>
       <c r="Q225" s="1">
@@ -17633,7 +17456,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="226" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A226" s="4">
         <v>8</v>
       </c>
@@ -17664,7 +17487,7 @@
       <c r="J226" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K226" s="1">
+      <c r="K226" s="2">
         <v>0</v>
       </c>
       <c r="L226" s="1" t="s">
@@ -17679,7 +17502,7 @@
       <c r="O226" s="1">
         <v>0</v>
       </c>
-      <c r="P226" s="1">
+      <c r="P226" s="2">
         <v>2</v>
       </c>
       <c r="Q226" s="1">
@@ -17696,7 +17519,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="227" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A227" s="4">
         <v>8</v>
       </c>
@@ -17727,7 +17550,7 @@
       <c r="J227" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K227" s="1">
+      <c r="K227" s="2">
         <v>0</v>
       </c>
       <c r="L227" s="1" t="s">
@@ -17742,7 +17565,7 @@
       <c r="O227" s="1">
         <v>0</v>
       </c>
-      <c r="P227" s="1">
+      <c r="P227" s="2">
         <v>2</v>
       </c>
       <c r="Q227" s="1">
@@ -17759,7 +17582,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="228" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A228" s="4">
         <v>8</v>
       </c>
@@ -17790,7 +17613,7 @@
       <c r="J228" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K228" s="1">
+      <c r="K228" s="2">
         <v>0</v>
       </c>
       <c r="L228" s="1" t="s">
@@ -17805,7 +17628,7 @@
       <c r="O228" s="1">
         <v>0</v>
       </c>
-      <c r="P228" s="1">
+      <c r="P228" s="2">
         <v>2</v>
       </c>
       <c r="Q228" s="1">
@@ -17822,7 +17645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="229" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A229" s="4">
         <v>8</v>
       </c>
@@ -17853,7 +17676,7 @@
       <c r="J229" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K229" s="1">
+      <c r="K229" s="2">
         <v>0</v>
       </c>
       <c r="L229" s="1" t="s">
@@ -17868,7 +17691,7 @@
       <c r="O229" s="1">
         <v>0</v>
       </c>
-      <c r="P229" s="1">
+      <c r="P229" s="2">
         <v>2</v>
       </c>
       <c r="Q229" s="1">
@@ -17885,7 +17708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="230" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A230" s="4">
         <v>8</v>
       </c>
@@ -17916,7 +17739,7 @@
       <c r="J230" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K230" s="1">
+      <c r="K230" s="2">
         <v>0</v>
       </c>
       <c r="L230" s="1" t="s">
@@ -17931,7 +17754,7 @@
       <c r="O230" s="1">
         <v>0</v>
       </c>
-      <c r="P230" s="1">
+      <c r="P230" s="2">
         <v>2</v>
       </c>
       <c r="Q230" s="1">
@@ -17979,7 +17802,7 @@
       <c r="J231" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K231" s="1" t="s">
+      <c r="K231" s="2" t="s">
         <v>582</v>
       </c>
       <c r="L231" s="1" t="s">
@@ -17994,7 +17817,7 @@
       <c r="O231" s="1">
         <v>0</v>
       </c>
-      <c r="P231" s="1">
+      <c r="P231" s="2">
         <v>2</v>
       </c>
       <c r="Q231" s="1">
@@ -18042,7 +17865,7 @@
       <c r="J232" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K232" s="1" t="s">
+      <c r="K232" s="2" t="s">
         <v>587</v>
       </c>
       <c r="L232" s="1" t="s">
@@ -18057,7 +17880,7 @@
       <c r="O232" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="P232" s="1">
+      <c r="P232" s="2">
         <v>2</v>
       </c>
       <c r="Q232" s="1">
@@ -18074,7 +17897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A233" s="4">
         <v>8</v>
       </c>
@@ -18105,7 +17928,7 @@
       <c r="J233" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K233" s="1">
+      <c r="K233" s="2">
         <v>0</v>
       </c>
       <c r="L233" s="1" t="s">
@@ -18120,7 +17943,7 @@
       <c r="O233" s="1">
         <v>0</v>
       </c>
-      <c r="P233" s="1">
+      <c r="P233" s="2">
         <v>2</v>
       </c>
       <c r="Q233" s="1">
@@ -18137,7 +17960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A234" s="4">
         <v>8</v>
       </c>
@@ -18168,7 +17991,7 @@
       <c r="J234" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K234" s="1">
+      <c r="K234" s="2">
         <v>0</v>
       </c>
       <c r="L234" s="1" t="s">
@@ -18183,7 +18006,7 @@
       <c r="O234" s="1">
         <v>0</v>
       </c>
-      <c r="P234" s="1" t="s">
+      <c r="P234" s="2" t="s">
         <v>429</v>
       </c>
       <c r="Q234" s="1">
@@ -18231,7 +18054,7 @@
       <c r="J235" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K235" s="1" t="s">
+      <c r="K235" s="2" t="s">
         <v>597</v>
       </c>
       <c r="L235" s="1" t="s">
@@ -18246,7 +18069,7 @@
       <c r="O235" s="1">
         <v>0</v>
       </c>
-      <c r="P235" s="1" t="s">
+      <c r="P235" s="2" t="s">
         <v>599</v>
       </c>
       <c r="Q235" s="1">
@@ -18294,7 +18117,7 @@
       <c r="J236" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="K236" s="1" t="s">
+      <c r="K236" s="2" t="s">
         <v>601</v>
       </c>
       <c r="L236" s="1" t="s">
@@ -18309,7 +18132,7 @@
       <c r="O236" s="1">
         <v>0</v>
       </c>
-      <c r="P236" s="1" t="s">
+      <c r="P236" s="2" t="s">
         <v>605</v>
       </c>
       <c r="Q236" s="1">
@@ -18357,7 +18180,7 @@
       <c r="J237" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K237" s="1" t="s">
+      <c r="K237" s="2" t="s">
         <v>606</v>
       </c>
       <c r="L237" s="1">
@@ -18372,7 +18195,7 @@
       <c r="O237" s="1">
         <v>0</v>
       </c>
-      <c r="P237" s="1" t="s">
+      <c r="P237" s="2" t="s">
         <v>599</v>
       </c>
       <c r="Q237" s="1">
@@ -18389,7 +18212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A238" s="4">
         <v>8</v>
       </c>
@@ -18420,7 +18243,7 @@
       <c r="J238" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K238" s="1">
+      <c r="K238" s="2">
         <v>0</v>
       </c>
       <c r="L238" s="1" t="s">
@@ -18435,7 +18258,7 @@
       <c r="O238" s="1">
         <v>0</v>
       </c>
-      <c r="P238" s="1" t="s">
+      <c r="P238" s="2" t="s">
         <v>599</v>
       </c>
       <c r="Q238" s="1">
@@ -18452,7 +18275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A239" s="4">
         <v>8</v>
       </c>
@@ -18483,7 +18306,7 @@
       <c r="J239" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K239" s="1">
+      <c r="K239" s="2">
         <v>0</v>
       </c>
       <c r="L239" s="1" t="s">
@@ -18498,7 +18321,7 @@
       <c r="O239" s="1">
         <v>0</v>
       </c>
-      <c r="P239" s="1" t="s">
+      <c r="P239" s="2" t="s">
         <v>599</v>
       </c>
       <c r="Q239" s="1">
@@ -18515,7 +18338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A240" s="4">
         <v>8</v>
       </c>
@@ -18546,7 +18369,7 @@
       <c r="J240" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K240" s="1">
+      <c r="K240" s="2">
         <v>0</v>
       </c>
       <c r="L240" s="1">
@@ -18561,7 +18384,7 @@
       <c r="O240" s="1">
         <v>0</v>
       </c>
-      <c r="P240" s="1" t="s">
+      <c r="P240" s="2" t="s">
         <v>599</v>
       </c>
       <c r="Q240" s="1">
@@ -18609,7 +18432,7 @@
       <c r="J241" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K241" s="1" t="s">
+      <c r="K241" s="2" t="s">
         <v>613</v>
       </c>
       <c r="L241" s="1">
@@ -18624,7 +18447,7 @@
       <c r="O241" s="1">
         <v>0</v>
       </c>
-      <c r="P241" s="1" t="s">
+      <c r="P241" s="2" t="s">
         <v>599</v>
       </c>
       <c r="Q241" s="1">
@@ -18672,7 +18495,7 @@
       <c r="J242" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="K242" s="1" t="s">
+      <c r="K242" s="2" t="s">
         <v>616</v>
       </c>
       <c r="L242" s="1" t="s">
@@ -18687,7 +18510,7 @@
       <c r="O242" s="1">
         <v>0</v>
       </c>
-      <c r="P242" s="1" t="s">
+      <c r="P242" s="2" t="s">
         <v>618</v>
       </c>
       <c r="Q242" s="1">
@@ -18704,7 +18527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A243" s="4">
         <v>8</v>
       </c>
@@ -18735,7 +18558,7 @@
       <c r="J243" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="K243" s="1">
+      <c r="K243" s="2">
         <v>0</v>
       </c>
       <c r="L243" s="1">
@@ -18750,7 +18573,7 @@
       <c r="O243" s="1">
         <v>0</v>
       </c>
-      <c r="P243" s="1" t="s">
+      <c r="P243" s="2" t="s">
         <v>618</v>
       </c>
       <c r="Q243" s="1">
@@ -18798,7 +18621,7 @@
       <c r="J244" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K244" s="1" t="s">
+      <c r="K244" s="2" t="s">
         <v>622</v>
       </c>
       <c r="L244" s="1" t="s">
@@ -18813,7 +18636,7 @@
       <c r="O244" s="1">
         <v>0</v>
       </c>
-      <c r="P244" s="1">
+      <c r="P244" s="2">
         <v>2</v>
       </c>
       <c r="Q244" s="1">
@@ -18861,7 +18684,7 @@
       <c r="J245" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K245" s="1" t="s">
+      <c r="K245" s="2" t="s">
         <v>626</v>
       </c>
       <c r="L245" s="1" t="s">
@@ -18876,7 +18699,7 @@
       <c r="O245" s="1">
         <v>0</v>
       </c>
-      <c r="P245" s="1">
+      <c r="P245" s="2">
         <v>2</v>
       </c>
       <c r="Q245" s="1">
@@ -18893,7 +18716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A246" s="4">
         <v>8</v>
       </c>
@@ -18924,7 +18747,7 @@
       <c r="J246" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K246" s="1">
+      <c r="K246" s="2">
         <v>0</v>
       </c>
       <c r="L246" s="1" t="s">
@@ -18939,7 +18762,7 @@
       <c r="O246" s="1">
         <v>0</v>
       </c>
-      <c r="P246" s="1">
+      <c r="P246" s="2">
         <v>2</v>
       </c>
       <c r="Q246" s="1">
@@ -18956,7 +18779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A247" s="4">
         <v>8</v>
       </c>
@@ -18987,7 +18810,7 @@
       <c r="J247" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K247" s="1">
+      <c r="K247" s="2">
         <v>0</v>
       </c>
       <c r="L247" s="1" t="s">
@@ -19002,7 +18825,7 @@
       <c r="O247" s="1">
         <v>0</v>
       </c>
-      <c r="P247" s="1">
+      <c r="P247" s="2">
         <v>2</v>
       </c>
       <c r="Q247" s="1">
@@ -19050,7 +18873,7 @@
       <c r="J248" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K248" s="1" t="s">
+      <c r="K248" s="2" t="s">
         <v>634</v>
       </c>
       <c r="L248" s="1" t="s">
@@ -19065,7 +18888,7 @@
       <c r="O248" s="1">
         <v>0</v>
       </c>
-      <c r="P248" s="1">
+      <c r="P248" s="2">
         <v>2</v>
       </c>
       <c r="Q248" s="1">
@@ -19113,7 +18936,7 @@
       <c r="J249" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K249" s="1" t="s">
+      <c r="K249" s="2" t="s">
         <v>638</v>
       </c>
       <c r="L249" s="1">
@@ -19128,7 +18951,7 @@
       <c r="O249" s="1">
         <v>0</v>
       </c>
-      <c r="P249" s="1">
+      <c r="P249" s="2">
         <v>2</v>
       </c>
       <c r="Q249" s="1">
@@ -19176,7 +18999,7 @@
       <c r="J250" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K250" s="1" t="s">
+      <c r="K250" s="2" t="s">
         <v>641</v>
       </c>
       <c r="L250" s="1">
@@ -19191,7 +19014,7 @@
       <c r="O250" s="1">
         <v>0</v>
       </c>
-      <c r="P250" s="1">
+      <c r="P250" s="2">
         <v>2</v>
       </c>
       <c r="Q250" s="1">
@@ -19208,7 +19031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A251" s="4">
         <v>8</v>
       </c>
@@ -19239,7 +19062,7 @@
       <c r="J251" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="K251" s="1">
+      <c r="K251" s="2">
         <v>0</v>
       </c>
       <c r="L251" s="1" t="s">
@@ -19254,7 +19077,7 @@
       <c r="O251" s="1">
         <v>0</v>
       </c>
-      <c r="P251" s="1" t="s">
+      <c r="P251" s="2" t="s">
         <v>645</v>
       </c>
       <c r="Q251" s="1">
@@ -19302,7 +19125,7 @@
       <c r="J252" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K252" s="1" t="s">
+      <c r="K252" s="2" t="s">
         <v>647</v>
       </c>
       <c r="L252" s="1" t="s">
@@ -19317,7 +19140,7 @@
       <c r="O252" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="P252" s="1" t="s">
+      <c r="P252" s="2" t="s">
         <v>651</v>
       </c>
       <c r="Q252" s="1">
@@ -19365,7 +19188,7 @@
       <c r="J253" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K253" s="1" t="s">
+      <c r="K253" s="2" t="s">
         <v>653</v>
       </c>
       <c r="L253" s="1" t="s">
@@ -19380,7 +19203,7 @@
       <c r="O253" s="1">
         <v>0</v>
       </c>
-      <c r="P253" s="1" t="s">
+      <c r="P253" s="2" t="s">
         <v>656</v>
       </c>
       <c r="Q253" s="1">
@@ -19428,7 +19251,7 @@
       <c r="J254" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K254" s="1" t="s">
+      <c r="K254" s="2" t="s">
         <v>657</v>
       </c>
       <c r="L254" s="1">
@@ -19443,7 +19266,7 @@
       <c r="O254" s="1">
         <v>0</v>
       </c>
-      <c r="P254" s="1">
+      <c r="P254" s="2">
         <v>2</v>
       </c>
       <c r="Q254" s="1">
@@ -19491,7 +19314,7 @@
       <c r="J255" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K255" s="1" t="s">
+      <c r="K255" s="2" t="s">
         <v>660</v>
       </c>
       <c r="L255" s="1" t="s">
@@ -19506,7 +19329,7 @@
       <c r="O255" s="1">
         <v>0</v>
       </c>
-      <c r="P255" s="1">
+      <c r="P255" s="2">
         <v>2</v>
       </c>
       <c r="Q255" s="1">
@@ -19554,7 +19377,7 @@
       <c r="J256" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="K256" s="1" t="s">
+      <c r="K256" s="2" t="s">
         <v>665</v>
       </c>
       <c r="L256" s="1" t="s">
@@ -19569,7 +19392,7 @@
       <c r="O256" s="1">
         <v>0</v>
       </c>
-      <c r="P256" s="1">
+      <c r="P256" s="2">
         <v>7</v>
       </c>
       <c r="Q256" s="1">
@@ -19617,7 +19440,7 @@
       <c r="J257" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="K257" s="1" t="s">
+      <c r="K257" s="7" t="s">
         <v>667</v>
       </c>
       <c r="L257" s="1" t="s">
@@ -19632,7 +19455,7 @@
       <c r="O257" s="1">
         <v>0</v>
       </c>
-      <c r="P257" s="1" t="s">
+      <c r="P257" s="2" t="s">
         <v>669</v>
       </c>
       <c r="Q257" s="1">
@@ -19680,7 +19503,7 @@
       <c r="J258" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="K258" s="1" t="s">
+      <c r="K258" s="2" t="s">
         <v>670</v>
       </c>
       <c r="L258" s="1">
@@ -19695,7 +19518,7 @@
       <c r="O258" s="1">
         <v>0</v>
       </c>
-      <c r="P258" s="1" t="s">
+      <c r="P258" s="2" t="s">
         <v>671</v>
       </c>
       <c r="Q258" s="1">
@@ -19743,7 +19566,7 @@
       <c r="J259" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="K259" s="1" t="s">
+      <c r="K259" s="2" t="s">
         <v>672</v>
       </c>
       <c r="L259" s="1" t="s">
@@ -19758,7 +19581,7 @@
       <c r="O259" s="1">
         <v>0</v>
       </c>
-      <c r="P259" s="1" t="s">
+      <c r="P259" s="2" t="s">
         <v>656</v>
       </c>
       <c r="Q259" s="1">
@@ -19806,7 +19629,7 @@
       <c r="J260" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="K260" s="1" t="s">
+      <c r="K260" s="2" t="s">
         <v>674</v>
       </c>
       <c r="L260" s="1" t="s">
@@ -19821,7 +19644,7 @@
       <c r="O260" s="1">
         <v>0</v>
       </c>
-      <c r="P260" s="1" t="s">
+      <c r="P260" s="2" t="s">
         <v>669</v>
       </c>
       <c r="Q260" s="1">
@@ -19838,7 +19661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A261" s="4">
         <v>8</v>
       </c>
@@ -19869,7 +19692,7 @@
       <c r="J261" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="K261" s="1">
+      <c r="K261" s="2">
         <v>0</v>
       </c>
       <c r="L261" s="1" t="s">
@@ -19884,7 +19707,7 @@
       <c r="O261" s="1">
         <v>0</v>
       </c>
-      <c r="P261" s="1" t="s">
+      <c r="P261" s="2" t="s">
         <v>656</v>
       </c>
       <c r="Q261" s="1">
@@ -19932,7 +19755,7 @@
       <c r="J262" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K262" s="1" t="s">
+      <c r="K262" s="2" t="s">
         <v>677</v>
       </c>
       <c r="L262" s="1" t="s">
@@ -19947,7 +19770,7 @@
       <c r="O262" s="1">
         <v>0</v>
       </c>
-      <c r="P262" s="1" t="s">
+      <c r="P262" s="2" t="s">
         <v>651</v>
       </c>
       <c r="Q262" s="1">
@@ -19995,7 +19818,7 @@
       <c r="J263" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="K263" s="1" t="s">
+      <c r="K263" s="2" t="s">
         <v>680</v>
       </c>
       <c r="L263" s="1" t="s">
@@ -20010,7 +19833,7 @@
       <c r="O263" s="1">
         <v>0</v>
       </c>
-      <c r="P263" s="1" t="s">
+      <c r="P263" s="2" t="s">
         <v>682</v>
       </c>
       <c r="Q263" s="1">
@@ -20058,7 +19881,7 @@
       <c r="J264" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="K264" s="1" t="s">
+      <c r="K264" s="2" t="s">
         <v>684</v>
       </c>
       <c r="L264" s="1">
@@ -20073,7 +19896,7 @@
       <c r="O264" s="1">
         <v>0</v>
       </c>
-      <c r="P264" s="1" t="s">
+      <c r="P264" s="2" t="s">
         <v>685</v>
       </c>
       <c r="Q264" s="1">
@@ -20121,7 +19944,7 @@
       <c r="J265" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="K265" s="1" t="s">
+      <c r="K265" s="7" t="s">
         <v>686</v>
       </c>
       <c r="L265" s="1" t="s">
@@ -20136,7 +19959,7 @@
       <c r="O265" s="1">
         <v>0</v>
       </c>
-      <c r="P265" s="1" t="s">
+      <c r="P265" s="2" t="s">
         <v>685</v>
       </c>
       <c r="Q265" s="1">
@@ -20153,7 +19976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A266" s="4">
         <v>9</v>
       </c>
@@ -20184,7 +20007,7 @@
       <c r="J266" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="K266" s="1">
+      <c r="K266" s="2">
         <v>0</v>
       </c>
       <c r="L266" s="1" t="s">
@@ -20199,7 +20022,7 @@
       <c r="O266" s="1">
         <v>0</v>
       </c>
-      <c r="P266" s="1" t="s">
+      <c r="P266" s="2" t="s">
         <v>685</v>
       </c>
       <c r="Q266" s="1">
@@ -20247,7 +20070,7 @@
       <c r="J267" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="K267" s="1" t="s">
+      <c r="K267" s="2" t="s">
         <v>690</v>
       </c>
       <c r="L267" s="1" t="s">
@@ -20262,7 +20085,7 @@
       <c r="O267" s="1">
         <v>0</v>
       </c>
-      <c r="P267" s="1" t="s">
+      <c r="P267" s="2" t="s">
         <v>685</v>
       </c>
       <c r="Q267" s="1">
@@ -20310,7 +20133,7 @@
       <c r="J268" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="K268" s="1" t="s">
+      <c r="K268" s="2" t="s">
         <v>692</v>
       </c>
       <c r="L268" s="1" t="s">
@@ -20325,7 +20148,7 @@
       <c r="O268" s="1">
         <v>0</v>
       </c>
-      <c r="P268" s="1" t="s">
+      <c r="P268" s="2" t="s">
         <v>685</v>
       </c>
       <c r="Q268" s="1">
@@ -20342,7 +20165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A269" s="4">
         <v>9</v>
       </c>
@@ -20373,7 +20196,7 @@
       <c r="J269" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="K269" s="1">
+      <c r="K269" s="2">
         <v>0</v>
       </c>
       <c r="L269" s="1" t="s">
@@ -20388,7 +20211,7 @@
       <c r="O269" s="1">
         <v>0</v>
       </c>
-      <c r="P269" s="1" t="s">
+      <c r="P269" s="2" t="s">
         <v>685</v>
       </c>
       <c r="Q269" s="1">
@@ -20436,7 +20259,7 @@
       <c r="J270" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K270" s="1" t="s">
+      <c r="K270" s="2" t="s">
         <v>696</v>
       </c>
       <c r="L270" s="1" t="s">
@@ -20451,7 +20274,7 @@
       <c r="O270" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="P270" s="1">
+      <c r="P270" s="2">
         <v>5</v>
       </c>
       <c r="Q270" s="1">
@@ -20499,7 +20322,7 @@
       <c r="J271" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K271" s="1" t="s">
+      <c r="K271" s="2" t="s">
         <v>701</v>
       </c>
       <c r="L271" s="1" t="s">
@@ -20514,7 +20337,7 @@
       <c r="O271" s="1">
         <v>0</v>
       </c>
-      <c r="P271" s="1">
+      <c r="P271" s="2">
         <v>5</v>
       </c>
       <c r="Q271" s="1">
@@ -20531,7 +20354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A272" s="4">
         <v>10</v>
       </c>
@@ -20562,7 +20385,7 @@
       <c r="J272" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K272" s="1">
+      <c r="K272" s="2">
         <v>0</v>
       </c>
       <c r="L272" s="1" t="s">
@@ -20577,7 +20400,7 @@
       <c r="O272" s="1">
         <v>0</v>
       </c>
-      <c r="P272" s="1">
+      <c r="P272" s="2">
         <v>5</v>
       </c>
       <c r="Q272" s="1">
@@ -20625,7 +20448,7 @@
       <c r="J273" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K273" s="1" t="s">
+      <c r="K273" s="2" t="s">
         <v>705</v>
       </c>
       <c r="L273" s="1" t="s">
@@ -20640,7 +20463,7 @@
       <c r="O273" s="1">
         <v>0</v>
       </c>
-      <c r="P273" s="1">
+      <c r="P273" s="2">
         <v>5</v>
       </c>
       <c r="Q273" s="1">
@@ -20688,7 +20511,7 @@
       <c r="J274" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K274" s="1" t="s">
+      <c r="K274" s="2" t="s">
         <v>708</v>
       </c>
       <c r="L274" s="1" t="s">
@@ -20703,7 +20526,7 @@
       <c r="O274" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="P274" s="1">
+      <c r="P274" s="2">
         <v>5</v>
       </c>
       <c r="Q274" s="1">
@@ -20720,7 +20543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A275" s="4">
         <v>10</v>
       </c>
@@ -20751,7 +20574,7 @@
       <c r="J275" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K275" s="1">
+      <c r="K275" s="2">
         <v>0</v>
       </c>
       <c r="L275" s="1" t="s">
@@ -20766,7 +20589,7 @@
       <c r="O275" s="1">
         <v>0</v>
       </c>
-      <c r="P275" s="1">
+      <c r="P275" s="2">
         <v>5</v>
       </c>
       <c r="Q275" s="1">
@@ -20783,7 +20606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A276" s="4">
         <v>10</v>
       </c>
@@ -20814,7 +20637,7 @@
       <c r="J276" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K276" s="1">
+      <c r="K276" s="2">
         <v>0</v>
       </c>
       <c r="L276" s="1" t="s">
@@ -20829,7 +20652,7 @@
       <c r="O276" s="1">
         <v>0</v>
       </c>
-      <c r="P276" s="1">
+      <c r="P276" s="2">
         <v>5</v>
       </c>
       <c r="Q276" s="1">
@@ -20877,7 +20700,7 @@
       <c r="J277" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K277" s="1" t="s">
+      <c r="K277" s="2" t="s">
         <v>717</v>
       </c>
       <c r="L277" s="1" t="s">
@@ -20892,7 +20715,7 @@
       <c r="O277" s="1">
         <v>0</v>
       </c>
-      <c r="P277" s="1">
+      <c r="P277" s="2">
         <v>5</v>
       </c>
       <c r="Q277" s="1">
@@ -20909,7 +20732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A278" s="4">
         <v>10</v>
       </c>
@@ -20940,7 +20763,7 @@
       <c r="J278" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K278" s="1">
+      <c r="K278" s="2">
         <v>0</v>
       </c>
       <c r="L278" s="1" t="s">
@@ -20955,7 +20778,7 @@
       <c r="O278" s="1">
         <v>0</v>
       </c>
-      <c r="P278" s="1">
+      <c r="P278" s="2">
         <v>5</v>
       </c>
       <c r="Q278" s="1">
@@ -20972,7 +20795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A279" s="4">
         <v>10</v>
       </c>
@@ -21003,7 +20826,7 @@
       <c r="J279" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K279" s="1">
+      <c r="K279" s="2">
         <v>0</v>
       </c>
       <c r="L279" s="1" t="s">
@@ -21018,7 +20841,7 @@
       <c r="O279" s="1">
         <v>0</v>
       </c>
-      <c r="P279" s="1">
+      <c r="P279" s="2">
         <v>5</v>
       </c>
       <c r="Q279" s="1">
@@ -21035,7 +20858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="27.75" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:20" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A280" s="4">
         <v>10</v>
       </c>
@@ -21066,7 +20889,7 @@
       <c r="J280" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K280" s="1">
+      <c r="K280" s="2">
         <v>0</v>
       </c>
       <c r="L280" s="1" t="s">
@@ -21081,7 +20904,7 @@
       <c r="O280" s="1">
         <v>0</v>
       </c>
-      <c r="P280" s="1">
+      <c r="P280" s="2">
         <v>5</v>
       </c>
       <c r="Q280" s="1">
@@ -21098,7 +20921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:20" ht="27" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A281" s="4">
         <v>10</v>
       </c>
@@ -21129,7 +20952,7 @@
       <c r="J281" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K281" s="1">
+      <c r="K281" s="2">
         <v>0</v>
       </c>
       <c r="L281" s="1" t="s">
@@ -21144,7 +20967,7 @@
       <c r="O281" s="1">
         <v>0</v>
       </c>
-      <c r="P281" s="1" t="s">
+      <c r="P281" s="2" t="s">
         <v>214</v>
       </c>
       <c r="Q281" s="1">
@@ -21161,7 +20984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A282" s="4">
         <v>10</v>
       </c>
@@ -21192,7 +21015,7 @@
       <c r="J282" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K282" s="1">
+      <c r="K282" s="2">
         <v>0</v>
       </c>
       <c r="L282" s="1" t="s">
@@ -21207,7 +21030,7 @@
       <c r="O282" s="1">
         <v>0</v>
       </c>
-      <c r="P282" s="1">
+      <c r="P282" s="2">
         <v>5</v>
       </c>
       <c r="Q282" s="1">
@@ -21224,7 +21047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A283" s="4">
         <v>10</v>
       </c>
@@ -21255,7 +21078,7 @@
       <c r="J283" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K283" s="1">
+      <c r="K283" s="2">
         <v>0</v>
       </c>
       <c r="L283" s="1" t="s">
@@ -21270,7 +21093,7 @@
       <c r="O283" s="1">
         <v>0</v>
       </c>
-      <c r="P283" s="1">
+      <c r="P283" s="2">
         <v>5</v>
       </c>
       <c r="Q283" s="1">
@@ -21287,7 +21110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A284" s="4">
         <v>10</v>
       </c>
@@ -21318,7 +21141,7 @@
       <c r="J284" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K284" s="1">
+      <c r="K284" s="2">
         <v>0</v>
       </c>
       <c r="L284" s="1" t="s">
@@ -21333,7 +21156,7 @@
       <c r="O284" s="1">
         <v>0</v>
       </c>
-      <c r="P284" s="1">
+      <c r="P284" s="2">
         <v>5</v>
       </c>
       <c r="Q284" s="1">
@@ -21381,7 +21204,7 @@
       <c r="J285" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K285" s="1" t="s">
+      <c r="K285" s="2" t="s">
         <v>730</v>
       </c>
       <c r="L285" s="1" t="s">
@@ -21396,7 +21219,7 @@
       <c r="O285" s="1">
         <v>0</v>
       </c>
-      <c r="P285" s="1">
+      <c r="P285" s="2">
         <v>5</v>
       </c>
       <c r="Q285" s="1">
@@ -21444,7 +21267,7 @@
       <c r="J286" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="K286" s="1" t="s">
+      <c r="K286" s="2" t="s">
         <v>733</v>
       </c>
       <c r="L286" s="1" t="s">
@@ -21459,7 +21282,7 @@
       <c r="O286" s="1">
         <v>0</v>
       </c>
-      <c r="P286" s="1" t="s">
+      <c r="P286" s="2" t="s">
         <v>656</v>
       </c>
       <c r="Q286" s="1">
@@ -21507,7 +21330,7 @@
       <c r="J287" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="K287" s="1" t="s">
+      <c r="K287" s="2" t="s">
         <v>735</v>
       </c>
       <c r="L287" s="1">
@@ -21522,7 +21345,7 @@
       <c r="O287" s="1">
         <v>0</v>
       </c>
-      <c r="P287" s="1" t="s">
+      <c r="P287" s="2" t="s">
         <v>736</v>
       </c>
       <c r="Q287" s="1">
@@ -21539,7 +21362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A288" s="4">
         <v>10</v>
       </c>
@@ -21570,7 +21393,7 @@
       <c r="J288" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="K288" s="1">
+      <c r="K288" s="2">
         <v>0</v>
       </c>
       <c r="L288" s="1">
@@ -21585,7 +21408,7 @@
       <c r="O288" s="1">
         <v>0</v>
       </c>
-      <c r="P288" s="1" t="s">
+      <c r="P288" s="2" t="s">
         <v>736</v>
       </c>
       <c r="Q288" s="1">
@@ -21602,7 +21425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A289" s="4">
         <v>10</v>
       </c>
@@ -21633,7 +21456,7 @@
       <c r="J289" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="K289" s="1">
+      <c r="K289" s="2">
         <v>0</v>
       </c>
       <c r="L289" s="1" t="s">
@@ -21648,7 +21471,7 @@
       <c r="O289" s="1">
         <v>0</v>
       </c>
-      <c r="P289" s="1" t="s">
+      <c r="P289" s="2" t="s">
         <v>736</v>
       </c>
       <c r="Q289" s="1">
@@ -21696,7 +21519,7 @@
       <c r="J290" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K290" s="1" t="s">
+      <c r="K290" s="2" t="s">
         <v>740</v>
       </c>
       <c r="L290" s="1" t="s">
@@ -21711,7 +21534,7 @@
       <c r="O290" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="P290" s="1">
+      <c r="P290" s="2">
         <v>5</v>
       </c>
       <c r="Q290" s="1">
@@ -21728,7 +21551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A291" s="4">
         <v>10</v>
       </c>
@@ -21759,7 +21582,7 @@
       <c r="J291" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K291" s="1">
+      <c r="K291" s="2">
         <v>0</v>
       </c>
       <c r="L291" s="1" t="s">
@@ -21774,7 +21597,7 @@
       <c r="O291" s="1">
         <v>0</v>
       </c>
-      <c r="P291" s="1">
+      <c r="P291" s="2">
         <v>5</v>
       </c>
       <c r="Q291" s="1">
@@ -21791,7 +21614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A292" s="4">
         <v>10</v>
       </c>
@@ -21822,7 +21645,7 @@
       <c r="J292" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K292" s="1">
+      <c r="K292" s="2">
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
@@ -21837,7 +21660,7 @@
       <c r="O292" s="1">
         <v>0</v>
       </c>
-      <c r="P292" s="1">
+      <c r="P292" s="2">
         <v>5</v>
       </c>
       <c r="Q292" s="1">
@@ -21854,7 +21677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A293" s="4">
         <v>10</v>
       </c>
@@ -21885,7 +21708,7 @@
       <c r="J293" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K293" s="1">
+      <c r="K293" s="2">
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
@@ -21900,7 +21723,7 @@
       <c r="O293" s="1">
         <v>0</v>
       </c>
-      <c r="P293" s="1">
+      <c r="P293" s="2">
         <v>5</v>
       </c>
       <c r="Q293" s="1">
@@ -21917,7 +21740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A294" s="4">
         <v>10</v>
       </c>
@@ -21948,7 +21771,7 @@
       <c r="J294" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="K294" s="1">
+      <c r="K294" s="2">
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
@@ -21963,7 +21786,7 @@
       <c r="O294" s="1">
         <v>0</v>
       </c>
-      <c r="P294" s="1">
+      <c r="P294" s="2">
         <v>5</v>
       </c>
       <c r="Q294" s="1">
@@ -22011,7 +21834,7 @@
       <c r="J295" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="K295" s="1" t="s">
+      <c r="K295" s="2" t="s">
         <v>751</v>
       </c>
       <c r="L295" s="1" t="s">
@@ -22026,7 +21849,7 @@
       <c r="O295" s="1">
         <v>0</v>
       </c>
-      <c r="P295" s="1" t="s">
+      <c r="P295" s="2" t="s">
         <v>754</v>
       </c>
       <c r="Q295" s="1">
@@ -22074,7 +21897,7 @@
       <c r="J296" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="K296" s="1" t="s">
+      <c r="K296" s="2" t="s">
         <v>757</v>
       </c>
       <c r="L296" s="1" t="s">
@@ -22089,7 +21912,7 @@
       <c r="O296" s="1">
         <v>0</v>
       </c>
-      <c r="P296" s="1" t="s">
+      <c r="P296" s="2" t="s">
         <v>759</v>
       </c>
       <c r="Q296" s="1">
@@ -22137,7 +21960,7 @@
       <c r="J297" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="K297" s="1" t="s">
+      <c r="K297" s="2" t="s">
         <v>760</v>
       </c>
       <c r="L297" s="1" t="s">
@@ -22152,7 +21975,7 @@
       <c r="O297" s="1">
         <v>0</v>
       </c>
-      <c r="P297" s="1" t="s">
+      <c r="P297" s="2" t="s">
         <v>759</v>
       </c>
       <c r="Q297" s="1">
@@ -22200,7 +22023,7 @@
       <c r="J298" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="K298" s="1" t="s">
+      <c r="K298" s="2" t="s">
         <v>764</v>
       </c>
       <c r="L298" s="1" t="s">
@@ -22215,7 +22038,7 @@
       <c r="O298" s="1">
         <v>0</v>
       </c>
-      <c r="P298" s="1" t="s">
+      <c r="P298" s="2" t="s">
         <v>767</v>
       </c>
       <c r="Q298" s="1">
@@ -22263,7 +22086,7 @@
       <c r="J299" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="K299" s="1" t="s">
+      <c r="K299" s="2" t="s">
         <v>768</v>
       </c>
       <c r="L299" s="1" t="s">
@@ -22278,7 +22101,7 @@
       <c r="O299" s="1">
         <v>0</v>
       </c>
-      <c r="P299" s="1" t="s">
+      <c r="P299" s="2" t="s">
         <v>767</v>
       </c>
       <c r="Q299" s="1">
@@ -22295,7 +22118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A300" s="4">
         <v>11</v>
       </c>
@@ -22326,7 +22149,7 @@
       <c r="J300" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="K300" s="1">
+      <c r="K300" s="2">
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
@@ -22341,7 +22164,7 @@
       <c r="O300" s="1">
         <v>0</v>
       </c>
-      <c r="P300" s="1" t="s">
+      <c r="P300" s="2" t="s">
         <v>767</v>
       </c>
       <c r="Q300" s="1">
@@ -22389,7 +22212,7 @@
       <c r="J301" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K301" s="1" t="s">
+      <c r="K301" s="2" t="s">
         <v>773</v>
       </c>
       <c r="L301" s="1">
@@ -22404,7 +22227,7 @@
       <c r="O301" s="1">
         <v>0</v>
       </c>
-      <c r="P301" s="1">
+      <c r="P301" s="2">
         <v>4</v>
       </c>
       <c r="Q301" s="1">
@@ -22452,7 +22275,7 @@
       <c r="J302" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K302" s="1" t="s">
+      <c r="K302" s="2" t="s">
         <v>774</v>
       </c>
       <c r="L302" s="1" t="s">
@@ -22467,7 +22290,7 @@
       <c r="O302" s="1">
         <v>0</v>
       </c>
-      <c r="P302" s="1">
+      <c r="P302" s="2">
         <v>4</v>
       </c>
       <c r="Q302" s="1">
@@ -22515,7 +22338,7 @@
       <c r="J303" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K303" s="1" t="s">
+      <c r="K303" s="2" t="s">
         <v>778</v>
       </c>
       <c r="L303" s="1" t="s">
@@ -22530,7 +22353,7 @@
       <c r="O303" s="1">
         <v>0</v>
       </c>
-      <c r="P303" s="1">
+      <c r="P303" s="2">
         <v>4</v>
       </c>
       <c r="Q303" s="1">
@@ -22578,7 +22401,7 @@
       <c r="J304" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K304" s="1" t="s">
+      <c r="K304" s="2" t="s">
         <v>781</v>
       </c>
       <c r="L304" s="1" t="s">
@@ -22593,7 +22416,7 @@
       <c r="O304" s="1">
         <v>0</v>
       </c>
-      <c r="P304" s="1" t="s">
+      <c r="P304" s="2" t="s">
         <v>784</v>
       </c>
       <c r="Q304" s="1">
@@ -22610,7 +22433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A305" s="4">
         <v>12</v>
       </c>
@@ -22641,7 +22464,7 @@
       <c r="J305" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K305" s="1">
+      <c r="K305" s="2">
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
@@ -22656,7 +22479,7 @@
       <c r="O305" s="1">
         <v>0</v>
       </c>
-      <c r="P305" s="1" t="s">
+      <c r="P305" s="2" t="s">
         <v>784</v>
       </c>
       <c r="Q305" s="1">
@@ -22704,7 +22527,7 @@
       <c r="J306" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K306" s="1" t="s">
+      <c r="K306" s="2" t="s">
         <v>786</v>
       </c>
       <c r="L306" s="1" t="s">
@@ -22719,7 +22542,7 @@
       <c r="O306" s="1">
         <v>0</v>
       </c>
-      <c r="P306" s="1" t="s">
+      <c r="P306" s="2" t="s">
         <v>789</v>
       </c>
       <c r="Q306" s="1">
@@ -22767,7 +22590,7 @@
       <c r="J307" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K307" s="1" t="s">
+      <c r="K307" s="2" t="s">
         <v>791</v>
       </c>
       <c r="L307" s="1" t="s">
@@ -22782,7 +22605,7 @@
       <c r="O307" s="1">
         <v>0</v>
       </c>
-      <c r="P307" s="1">
+      <c r="P307" s="2">
         <v>4</v>
       </c>
       <c r="Q307" s="1">
@@ -22799,7 +22622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A308" s="4">
         <v>12</v>
       </c>
@@ -22830,7 +22653,7 @@
       <c r="J308" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K308" s="1">
+      <c r="K308" s="2">
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
@@ -22845,7 +22668,7 @@
       <c r="O308" s="1">
         <v>0</v>
       </c>
-      <c r="P308" s="1">
+      <c r="P308" s="2">
         <v>4</v>
       </c>
       <c r="Q308" s="1">
@@ -22862,7 +22685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A309" s="4">
         <v>12</v>
       </c>
@@ -22893,7 +22716,7 @@
       <c r="J309" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K309" s="1">
+      <c r="K309" s="2">
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
@@ -22908,7 +22731,7 @@
       <c r="O309" s="1">
         <v>0</v>
       </c>
-      <c r="P309" s="1">
+      <c r="P309" s="2">
         <v>4</v>
       </c>
       <c r="Q309" s="1">
@@ -22925,7 +22748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A310" s="4">
         <v>12</v>
       </c>
@@ -22956,7 +22779,7 @@
       <c r="J310" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K310" s="1">
+      <c r="K310" s="2">
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
@@ -22971,7 +22794,7 @@
       <c r="O310" s="1">
         <v>0</v>
       </c>
-      <c r="P310" s="1">
+      <c r="P310" s="2">
         <v>4</v>
       </c>
       <c r="Q310" s="1">
@@ -23019,7 +22842,7 @@
       <c r="J311" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K311" s="1" t="s">
+      <c r="K311" s="2" t="s">
         <v>800</v>
       </c>
       <c r="L311" s="1" t="s">
@@ -23034,7 +22857,7 @@
       <c r="O311" s="1">
         <v>0</v>
       </c>
-      <c r="P311" s="1">
+      <c r="P311" s="2">
         <v>4</v>
       </c>
       <c r="Q311" s="1">
@@ -23082,7 +22905,7 @@
       <c r="J312" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K312" s="1" t="s">
+      <c r="K312" s="2" t="s">
         <v>803</v>
       </c>
       <c r="L312" s="1" t="s">
@@ -23097,7 +22920,7 @@
       <c r="O312" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="P312" s="1">
+      <c r="P312" s="2">
         <v>4</v>
       </c>
       <c r="Q312" s="1">
@@ -23114,7 +22937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A313" s="4">
         <v>12</v>
       </c>
@@ -23145,7 +22968,7 @@
       <c r="J313" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K313" s="1">
+      <c r="K313" s="2">
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
@@ -23160,7 +22983,7 @@
       <c r="O313" s="1">
         <v>0</v>
       </c>
-      <c r="P313" s="1">
+      <c r="P313" s="2">
         <v>4</v>
       </c>
       <c r="Q313" s="1">
@@ -23208,7 +23031,7 @@
       <c r="J314" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="K314" s="1" t="s">
+      <c r="K314" s="2" t="s">
         <v>810</v>
       </c>
       <c r="L314" s="1">
@@ -23223,7 +23046,7 @@
       <c r="O314" s="1">
         <v>0</v>
       </c>
-      <c r="P314" s="1">
+      <c r="P314" s="2">
         <v>4</v>
       </c>
       <c r="Q314" s="1">
@@ -23271,7 +23094,7 @@
       <c r="J315" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K315" s="1" t="s">
+      <c r="K315" s="2" t="s">
         <v>813</v>
       </c>
       <c r="L315" s="1" t="s">
@@ -23286,7 +23109,7 @@
       <c r="O315" s="1">
         <v>0</v>
       </c>
-      <c r="P315" s="1">
+      <c r="P315" s="2">
         <v>5</v>
       </c>
       <c r="Q315" s="1">
@@ -23303,7 +23126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A316" s="4">
         <v>13</v>
       </c>
@@ -23334,7 +23157,7 @@
       <c r="J316" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K316" s="1">
+      <c r="K316" s="2">
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
@@ -23349,7 +23172,7 @@
       <c r="O316" s="1">
         <v>0</v>
       </c>
-      <c r="P316" s="1">
+      <c r="P316" s="2">
         <v>5</v>
       </c>
       <c r="Q316" s="1">
@@ -23397,7 +23220,7 @@
       <c r="J317" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K317" s="1" t="s">
+      <c r="K317" s="2" t="s">
         <v>818</v>
       </c>
       <c r="L317" s="1" t="s">
@@ -23412,7 +23235,7 @@
       <c r="O317" s="1">
         <v>0</v>
       </c>
-      <c r="P317" s="1">
+      <c r="P317" s="2">
         <v>5</v>
       </c>
       <c r="Q317" s="1">
@@ -23429,7 +23252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A318" s="4">
         <v>13</v>
       </c>
@@ -23460,7 +23283,7 @@
       <c r="J318" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K318" s="1">
+      <c r="K318" s="2">
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
@@ -23475,7 +23298,7 @@
       <c r="O318" s="1">
         <v>0</v>
       </c>
-      <c r="P318" s="1">
+      <c r="P318" s="2">
         <v>5</v>
       </c>
       <c r="Q318" s="1">
@@ -23523,7 +23346,7 @@
       <c r="J319" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K319" s="1" t="s">
+      <c r="K319" s="2" t="s">
         <v>823</v>
       </c>
       <c r="L319" s="1" t="s">
@@ -23538,7 +23361,7 @@
       <c r="O319" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="P319" s="1">
+      <c r="P319" s="2">
         <v>5</v>
       </c>
       <c r="Q319" s="1">
@@ -23555,7 +23378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A320" s="4">
         <v>13</v>
       </c>
@@ -23586,7 +23409,7 @@
       <c r="J320" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K320" s="1">
+      <c r="K320" s="2">
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
@@ -23601,7 +23424,7 @@
       <c r="O320" s="1">
         <v>0</v>
       </c>
-      <c r="P320" s="1">
+      <c r="P320" s="2">
         <v>5</v>
       </c>
       <c r="Q320" s="1">
@@ -23649,7 +23472,7 @@
       <c r="J321" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K321" s="1" t="s">
+      <c r="K321" s="2" t="s">
         <v>829</v>
       </c>
       <c r="L321" s="1">
@@ -23664,7 +23487,7 @@
       <c r="O321" s="1">
         <v>0</v>
       </c>
-      <c r="P321" s="1">
+      <c r="P321" s="2">
         <v>5</v>
       </c>
       <c r="Q321" s="1">
@@ -23681,7 +23504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A322" s="4">
         <v>13</v>
       </c>
@@ -23712,7 +23535,7 @@
       <c r="J322" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K322" s="1">
+      <c r="K322" s="2">
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
@@ -23727,7 +23550,7 @@
       <c r="O322" s="1">
         <v>0</v>
       </c>
-      <c r="P322" s="1">
+      <c r="P322" s="2">
         <v>5</v>
       </c>
       <c r="Q322" s="1">
@@ -23744,7 +23567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A323" s="4">
         <v>13</v>
       </c>
@@ -23775,7 +23598,7 @@
       <c r="J323" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K323" s="1">
+      <c r="K323" s="2">
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
@@ -23790,7 +23613,7 @@
       <c r="O323" s="1">
         <v>0</v>
       </c>
-      <c r="P323" s="1">
+      <c r="P323" s="2">
         <v>5</v>
       </c>
       <c r="Q323" s="1">
@@ -23807,7 +23630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A324" s="4">
         <v>13</v>
       </c>
@@ -23838,7 +23661,7 @@
       <c r="J324" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="K324" s="1">
+      <c r="K324" s="2">
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
@@ -23853,7 +23676,7 @@
       <c r="O324" s="1">
         <v>0</v>
       </c>
-      <c r="P324" s="1" t="s">
+      <c r="P324" s="2" t="s">
         <v>838</v>
       </c>
       <c r="Q324" s="1">
@@ -23901,7 +23724,7 @@
       <c r="J325" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="K325" s="1" t="s">
+      <c r="K325" s="2" t="s">
         <v>841</v>
       </c>
       <c r="L325" s="1" t="s">
@@ -23916,7 +23739,7 @@
       <c r="O325" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="P325" s="1">
+      <c r="P325" s="2">
         <v>6</v>
       </c>
       <c r="Q325" s="1">
@@ -23964,7 +23787,7 @@
       <c r="J326" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="K326" s="1" t="s">
+      <c r="K326" s="2" t="s">
         <v>846</v>
       </c>
       <c r="L326" s="1" t="s">
@@ -23979,7 +23802,7 @@
       <c r="O326" s="1">
         <v>0</v>
       </c>
-      <c r="P326" s="1" t="s">
+      <c r="P326" s="2" t="s">
         <v>849</v>
       </c>
       <c r="Q326" s="1">
@@ -23996,7 +23819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A327" s="4">
         <v>14</v>
       </c>
@@ -24027,7 +23850,7 @@
       <c r="J327" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="K327" s="1">
+      <c r="K327" s="2">
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
@@ -24042,7 +23865,7 @@
       <c r="O327" s="1">
         <v>0</v>
       </c>
-      <c r="P327" s="1" t="s">
+      <c r="P327" s="2" t="s">
         <v>789</v>
       </c>
       <c r="Q327" s="1">
@@ -24059,7 +23882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:20" hidden="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A328" s="4">
         <v>14</v>
       </c>
@@ -24090,7 +23913,7 @@
       <c r="J328" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="K328" s="1">
+      <c r="K328" s="2">
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
@@ -24105,7 +23928,7 @@
       <c r="O328" s="1">
         <v>0</v>
       </c>
-      <c r="P328" s="1" t="s">
+      <c r="P328" s="2" t="s">
         <v>789</v>
       </c>
       <c r="Q328" s="1">
@@ -24123,6 +23946,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
